--- a/Documents/HU, HT, PB, SB.xlsx
+++ b/Documents/HU, HT, PB, SB.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ff47571d30268be/Documentos/6/APLICACIONE II/Proyecto/SIGDCOLTA/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1529DF72-A3DE-466E-97C9-837D61FF45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{1529DF72-A3DE-466E-97C9-837D61FF45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A97973B-AEAA-4991-8C8B-B212378CB00D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{D7927580-9A21-4766-84F0-58BE9C7E4DF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="4" xr2:uid="{D7927580-9A21-4766-84F0-58BE9C7E4DF7}"/>
   </bookViews>
   <sheets>
-    <sheet name="HT" sheetId="3" r:id="rId1"/>
-    <sheet name="HU" sheetId="4" r:id="rId2"/>
-    <sheet name="PB" sheetId="1" r:id="rId3"/>
-    <sheet name="SB" sheetId="2" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId1"/>
+    <sheet name="HT" sheetId="3" r:id="rId2"/>
+    <sheet name="HU" sheetId="4" r:id="rId3"/>
+    <sheet name="PB" sheetId="1" r:id="rId4"/>
+    <sheet name="SB" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="566">
   <si>
     <t>Identificador (ID) de la Historia</t>
   </si>
@@ -381,9 +382,6 @@
     <t>La arquitectura definida debe ser escalable para futuras expansiones.</t>
   </si>
   <si>
-    <t>El modelo de base de datos debe reflejar con precisión la estructura requerida.</t>
-  </si>
-  <si>
     <t>La conexión de datos debe establecerse correctamente sin errores.</t>
   </si>
   <si>
@@ -426,9 +424,6 @@
     <t>Se deben establecer índices y claves foráneas según las mejores prácticas.</t>
   </si>
   <si>
-    <t>Las operaciones CRUD en la base de datos deben funcionar sin problemas.</t>
-  </si>
-  <si>
     <t>Las rutas deben estar configuradas correctamente para las operaciones principales.</t>
   </si>
   <si>
@@ -468,9 +463,6 @@
     <t>Se deben realizar pruebas de rendimiento en consultas de base de datos.</t>
   </si>
   <si>
-    <t>Se deben implementar mecanismos de manejo de errores en caso de falla de conexión.</t>
-  </si>
-  <si>
     <t>El backend debe manejar de manera efectiva los errores y excepciones.</t>
   </si>
   <si>
@@ -507,9 +499,6 @@
     <t>La documentación del modelo de datos debe estar actualizada.</t>
   </si>
   <si>
-    <t>Se debe realizar una prueba de estrés en la conexión de datos.</t>
-  </si>
-  <si>
     <t>Las funciones principales del backend deben estar cubiertas por pruebas unitarias.</t>
   </si>
   <si>
@@ -564,9 +553,6 @@
     <t>En caso de interrupciones temporales en la conexión.</t>
   </si>
   <si>
-    <t>En caso de que se prevean picos de carga en el sistema.</t>
-  </si>
-  <si>
     <t>En caso de cambios en las versiones de las dependencias.</t>
   </si>
   <si>
@@ -1428,9 +1414,6 @@
     <t>SB14</t>
   </si>
   <si>
-    <t>Implementar opción de registro mediante redes sociales</t>
-  </si>
-  <si>
     <t>Agregar verificación de correo electrónico al registro</t>
   </si>
   <si>
@@ -1729,13 +1712,37 @@
   </si>
   <si>
     <t>Al realizar operaciones CRUD mediante SQL en el entorno de desarrollo.</t>
+  </si>
+  <si>
+    <t>El modelo de base de datos debe reflejar la estructura requerida.</t>
+  </si>
+  <si>
+    <t>Investigacion Sobre el ORM de Laravel</t>
+  </si>
+  <si>
+    <t>Las operaciones CRUD en la base de datos</t>
+  </si>
+  <si>
+    <t>Se deben implementar mensajes de manejo de errores en caso de falla de conexión.</t>
+  </si>
+  <si>
+    <t>Se debe realizar una prueba de estrés en la conexión de datos y en las operaciones CRUD.</t>
+  </si>
+  <si>
+    <t>En caso de que se prevean errores de sistema</t>
+  </si>
+  <si>
+    <t>Implementar opción de registro mediante gmail</t>
+  </si>
+  <si>
+    <t>Sprint 3-4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1796,6 +1803,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1881,7 +1896,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -2108,11 +2123,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2286,6 +2332,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2319,6 +2371,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2394,21 +2455,22 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2722,8 +2784,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158A66CF-5D6C-4B15-B8B5-3066AF31B14F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9B023D-957F-4AAE-9E3E-1343C14F2EF3}">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="20" customWidth="1"/>
@@ -2740,18 +2811,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="87" t="s">
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="89"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="94"/>
     </row>
     <row r="2" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -2784,11 +2855,11 @@
     </row>
     <row r="3" spans="1:9" s="37" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -2796,16 +2867,16 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="79" t="s">
         <v>70</v>
       </c>
       <c r="E4" s="26">
@@ -2815,81 +2886,81 @@
         <v>112</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="74"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="79"/>
       <c r="E5" s="26">
         <v>2</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G5" s="23"/>
       <c r="H5" s="23" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="74"/>
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="79"/>
       <c r="E6" s="26">
         <v>3</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="74"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="79"/>
       <c r="E7" s="26">
         <v>4</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31"/>
-      <c r="B8" s="61" t="s">
-        <v>335</v>
-      </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63"/>
+      <c r="B8" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -2897,258 +2968,258 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="69" t="s">
         <v>77</v>
       </c>
       <c r="E9" s="26">
         <v>1</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="26">
         <v>2</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="26">
         <v>3</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="43"/>
       <c r="F12" s="23" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="43"/>
-      <c r="F13" s="97" t="s">
-        <v>554</v>
+      <c r="F13" s="61" t="s">
+        <v>548</v>
       </c>
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="43"/>
       <c r="F14" s="44" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="G14" s="44"/>
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
     </row>
     <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="26">
         <v>4</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
-      <c r="B16" s="64" t="s">
-        <v>337</v>
-      </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="66"/>
+      <c r="B16" s="66" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" s="67"/>
+      <c r="D16" s="68"/>
       <c r="E16" s="27"/>
-      <c r="F16" s="98"/>
+      <c r="F16" s="62"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="99" t="s">
+      <c r="C17" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="70" t="s">
         <v>81</v>
       </c>
       <c r="E17" s="26">
         <v>1</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="70"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="68"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="70"/>
       <c r="E18" s="26">
         <v>2</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="G18" s="23"/>
       <c r="H18" s="23" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="70"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="68"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="70"/>
       <c r="E19" s="43"/>
       <c r="F19" s="44" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="68"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="70"/>
       <c r="E20" s="26">
         <v>3</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="70"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="100"/>
-      <c r="D21" s="68"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="70"/>
       <c r="E21" s="26">
         <v>4</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="68"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="43"/>
       <c r="F22" s="44" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="G22" s="44"/>
       <c r="H22" s="44"/>
@@ -3156,11 +3227,11 @@
     </row>
     <row r="23" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
-      <c r="B23" s="61" t="s">
-        <v>333</v>
-      </c>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+      <c r="B23" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="64"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
@@ -3168,16 +3239,16 @@
       <c r="I23" s="28"/>
     </row>
     <row r="24" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="74" t="s">
+      <c r="D24" s="79" t="s">
         <v>73</v>
       </c>
       <c r="E24" s="26">
@@ -3188,78 +3259,78 @@
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="72"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="74"/>
+      <c r="A25" s="77"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="79"/>
       <c r="E25" s="34">
         <v>2</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="72"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="74"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="79"/>
       <c r="E26" s="26">
         <v>3</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="72"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="74"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
       <c r="E27" s="26">
         <v>4</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30"/>
-      <c r="B28" s="61" t="s">
-        <v>334</v>
-      </c>
-      <c r="C28" s="62"/>
-      <c r="D28" s="63"/>
+      <c r="B28" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" s="64"/>
+      <c r="D28" s="65"/>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
@@ -3267,1234 +3338,1250 @@
       <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="78" t="s">
+      <c r="C29" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="86" t="s">
         <v>75</v>
       </c>
       <c r="E29" s="26">
         <v>1</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>114</v>
+        <v>558</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="76"/>
-      <c r="B30" s="76"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="82"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="87"/>
       <c r="E30" s="26">
         <v>2</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="82"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="87"/>
       <c r="E31" s="26">
         <v>3</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="83"/>
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="26">
         <v>4</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
-      <c r="B33" s="64" t="s">
-        <v>336</v>
-      </c>
-      <c r="C33" s="65"/>
-      <c r="D33" s="66"/>
+      <c r="B33" s="66" t="s">
+        <v>331</v>
+      </c>
+      <c r="C33" s="67"/>
+      <c r="D33" s="68"/>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="28"/>
     </row>
-    <row r="34" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="69" t="s">
+    <row r="34" spans="1:9" s="103" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="67" t="s">
+      <c r="C34" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="67" t="s">
+      <c r="D34" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="34"/>
+      <c r="F34" s="102" t="s">
+        <v>559</v>
+      </c>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+    </row>
+    <row r="35" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="72"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="26">
         <v>1</v>
       </c>
-      <c r="F34" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="70"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="26">
-        <v>2</v>
-      </c>
       <c r="F35" s="23" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="72"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="26">
+        <v>2</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>560</v>
+      </c>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23" t="s">
+        <v>557</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="72"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="26">
+        <v>3</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="H37" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="73"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="26">
+        <v>4</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>562</v>
+      </c>
+      <c r="G38" s="23" t="s">
         <v>563</v>
       </c>
-      <c r="I35" s="23" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="70"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="26">
-        <v>3</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="71"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="26">
-        <v>4</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="32"/>
-      <c r="B38" s="64" t="s">
-        <v>338</v>
-      </c>
-      <c r="C38" s="65"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-    </row>
-    <row r="39" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="69" t="s">
+      <c r="H38" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="32"/>
+      <c r="B39" s="66" t="s">
+        <v>333</v>
+      </c>
+      <c r="C39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+    </row>
+    <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="68" t="s">
+      <c r="B40" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="67" t="s">
+      <c r="C40" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="67" t="s">
+      <c r="D40" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E40" s="26">
         <v>1</v>
       </c>
-      <c r="F39" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="26">
-        <v>2</v>
-      </c>
       <c r="F40" s="24" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="72"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="26">
+        <v>2</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="72"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="26">
+        <v>3</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="73"/>
+      <c r="B43" s="70"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="26">
+        <v>4</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="G43" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="32"/>
+      <c r="B44" s="66" t="s">
+        <v>334</v>
+      </c>
+      <c r="C44" s="67"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+    </row>
+    <row r="45" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="26">
+        <v>1</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="72"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="26">
+        <v>2</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="I46" s="24" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="72"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="26">
+        <v>3</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="H47" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="I40" s="24" t="s">
+      <c r="I47" s="24" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="70"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="26">
+    <row r="48" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="73"/>
+      <c r="B48" s="70"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="26">
+        <v>4</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="I48" s="24" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="32"/>
+      <c r="B49" s="66" t="s">
+        <v>335</v>
+      </c>
+      <c r="C49" s="67"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+    </row>
+    <row r="50" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="69" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="26">
+        <v>1</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="72"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="26">
+        <v>2</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="I51" s="24" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="72"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="26">
         <v>3</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F52" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="73"/>
+      <c r="B53" s="70"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="26">
+        <v>4</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="I53" s="24" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="32"/>
+      <c r="B54" s="66" t="s">
+        <v>336</v>
+      </c>
+      <c r="C54" s="67"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+    </row>
+    <row r="55" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="26">
+        <v>1</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="G55" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="I55" s="24" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="72"/>
+      <c r="B56" s="70"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="26">
+        <v>2</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="I56" s="24" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="72"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="26">
+        <v>3</v>
+      </c>
+      <c r="F57" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="G41" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41" s="24" t="s">
+      <c r="G57" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="H57" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="I57" s="24" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="73"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="26">
+        <v>4</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="H58" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="I41" s="24" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="26">
+      <c r="I58" s="24" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="32"/>
+      <c r="B59" s="66" t="s">
+        <v>337</v>
+      </c>
+      <c r="C59" s="67"/>
+      <c r="D59" s="68"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+    </row>
+    <row r="60" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="26">
+        <v>1</v>
+      </c>
+      <c r="F60" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="I60" s="24" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="72"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="26">
+        <v>2</v>
+      </c>
+      <c r="F61" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="H61" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="I61" s="24" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="72"/>
+      <c r="B62" s="70"/>
+      <c r="C62" s="69"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="26">
+        <v>3</v>
+      </c>
+      <c r="F62" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="H62" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="I62" s="24" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="73"/>
+      <c r="B63" s="70"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="26">
         <v>4</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F63" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="G42" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="32"/>
-      <c r="B43" s="64" t="s">
+      <c r="G63" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H63" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="I63" s="24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="32"/>
+      <c r="B64" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="C64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="33"/>
+    </row>
+    <row r="65" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C65" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" s="26">
+        <v>1</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="G65" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="H65" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I65" s="24" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="72"/>
+      <c r="B66" s="70"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="26">
+        <v>2</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="H66" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="I66" s="24" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="72"/>
+      <c r="B67" s="70"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="26">
+        <v>3</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="H67" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="I67" s="24" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="73"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="26">
+        <v>4</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="H68" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="I68" s="24" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="32"/>
+      <c r="B69" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="C43" s="65"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-    </row>
-    <row r="44" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="68" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" s="26">
+      <c r="C69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+    </row>
+    <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="E70" s="26">
         <v>1</v>
       </c>
-      <c r="F44" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="G44" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="70"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="67"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="26">
+      <c r="F70" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H70" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="I70" s="24" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="72"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="69"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="26">
         <v>2</v>
       </c>
-      <c r="F45" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="G45" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="I45" s="24" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="70"/>
-      <c r="B46" s="68"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="26">
-        <v>3</v>
-      </c>
-      <c r="F46" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G46" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="71"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="67"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="26">
-        <v>4</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="32"/>
-      <c r="B48" s="64" t="s">
-        <v>340</v>
-      </c>
-      <c r="C48" s="65"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-    </row>
-    <row r="49" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49" s="67" t="s">
-        <v>89</v>
-      </c>
-      <c r="E49" s="26">
-        <v>1</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="70"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="26">
-        <v>2</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="70"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="67"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="26">
-        <v>3</v>
-      </c>
-      <c r="F51" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="G51" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="I51" s="24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="71"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="67"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="26">
-        <v>4</v>
-      </c>
-      <c r="F52" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="G52" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="H52" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="I52" s="24" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="32"/>
-      <c r="B53" s="64" t="s">
-        <v>341</v>
-      </c>
-      <c r="C53" s="65"/>
-      <c r="D53" s="66"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-    </row>
-    <row r="54" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="67" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="E54" s="26">
-        <v>1</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="I54" s="24" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="70"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="26">
-        <v>2</v>
-      </c>
-      <c r="F55" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G55" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H55" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="I55" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="70"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="26">
-        <v>3</v>
-      </c>
-      <c r="F56" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="G56" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H56" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="I56" s="24" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="26">
-        <v>4</v>
-      </c>
-      <c r="F57" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="G57" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="H57" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="I57" s="24" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="32"/>
-      <c r="B58" s="64" t="s">
-        <v>342</v>
-      </c>
-      <c r="C58" s="65"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
-    </row>
-    <row r="59" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="67" t="s">
-        <v>93</v>
-      </c>
-      <c r="D59" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="E59" s="26">
-        <v>1</v>
-      </c>
-      <c r="F59" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="I59" s="24" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="70"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="26">
-        <v>2</v>
-      </c>
-      <c r="F60" s="24" t="s">
+      <c r="F71" s="24" t="s">
         <v>134</v>
-      </c>
-      <c r="G60" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="H60" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I60" s="24" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="70"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="26">
-        <v>3</v>
-      </c>
-      <c r="F61" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="G61" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="H61" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I61" s="24" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="26">
-        <v>4</v>
-      </c>
-      <c r="F62" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="G62" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="H62" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="I62" s="24" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="32"/>
-      <c r="B63" s="64" t="s">
-        <v>343</v>
-      </c>
-      <c r="C63" s="65"/>
-      <c r="D63" s="66"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-    </row>
-    <row r="64" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="68" t="s">
-        <v>95</v>
-      </c>
-      <c r="C64" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="D64" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="E64" s="26">
-        <v>1</v>
-      </c>
-      <c r="F64" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="G64" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="I64" s="24" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="70"/>
-      <c r="B65" s="68"/>
-      <c r="C65" s="67"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="26">
-        <v>2</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="G65" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="70"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="26">
-        <v>3</v>
-      </c>
-      <c r="F66" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="G66" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H66" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="I66" s="24" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="71"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="67"/>
-      <c r="D67" s="67"/>
-      <c r="E67" s="26">
-        <v>4</v>
-      </c>
-      <c r="F67" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="G67" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="I67" s="24" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="32"/>
-      <c r="B68" s="64" t="s">
-        <v>344</v>
-      </c>
-      <c r="C68" s="65"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="33"/>
-      <c r="G68" s="33"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="33"/>
-    </row>
-    <row r="69" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="C69" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="D69" s="67" t="s">
-        <v>101</v>
-      </c>
-      <c r="E69" s="26">
-        <v>1</v>
-      </c>
-      <c r="F69" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="G69" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="H69" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="I69" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="70"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="26">
-        <v>2</v>
-      </c>
-      <c r="F70" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="G70" s="24"/>
-      <c r="H70" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="I70" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="70"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="67"/>
-      <c r="D71" s="67"/>
-      <c r="E71" s="26">
-        <v>3</v>
-      </c>
-      <c r="F71" s="24" t="s">
-        <v>150</v>
       </c>
       <c r="G71" s="24"/>
       <c r="H71" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="I71" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="72"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="26">
+        <v>3</v>
+      </c>
+      <c r="F72" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="24"/>
+      <c r="H72" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="I72" s="24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="73"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="69"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="26">
+        <v>4</v>
+      </c>
+      <c r="F73" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G73" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H73" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I73" s="24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="32"/>
+      <c r="B74" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="C74" s="67"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="33"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="33"/>
+      <c r="I74" s="33"/>
+    </row>
+    <row r="75" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B75" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="C75" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="E75" s="26">
+        <v>1</v>
+      </c>
+      <c r="F75" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="G75" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="H75" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I75" s="24" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="72"/>
+      <c r="B76" s="70"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="26">
+        <v>2</v>
+      </c>
+      <c r="F76" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G76" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H76" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="I76" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="72"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="26">
+        <v>3</v>
+      </c>
+      <c r="F77" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G77" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="H77" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="I77" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="73"/>
+      <c r="B78" s="70"/>
+      <c r="C78" s="69"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="26">
+        <v>4</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="H78" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="I71" s="24" t="s">
+      <c r="I78" s="24" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="71"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="67"/>
-      <c r="D72" s="67"/>
-      <c r="E72" s="26">
+    <row r="79" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="32"/>
+      <c r="B79" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="C79" s="67"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="33"/>
+      <c r="G79" s="33"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="33"/>
+    </row>
+    <row r="80" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C80" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="26">
+        <v>1</v>
+      </c>
+      <c r="F80" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G80" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="H80" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="I80" s="24" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="72"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="26">
+        <v>2</v>
+      </c>
+      <c r="F81" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="G81" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="H81" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="I81" s="24" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="72"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="26">
+        <v>3</v>
+      </c>
+      <c r="F82" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="G82" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H82" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="I82" s="24" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="73"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="69"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="26">
         <v>4</v>
       </c>
-      <c r="F72" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="G72" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="I72" s="24" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="32"/>
-      <c r="B73" s="64" t="s">
-        <v>345</v>
-      </c>
-      <c r="C73" s="65"/>
-      <c r="D73" s="66"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="33"/>
-    </row>
-    <row r="74" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="69" t="s">
-        <v>102</v>
-      </c>
-      <c r="B74" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="C74" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D74" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="E74" s="26">
+      <c r="F83" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G83" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="I83" s="24" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="32"/>
+      <c r="B84" s="66" t="s">
+        <v>342</v>
+      </c>
+      <c r="C84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="33"/>
+      <c r="G84" s="33"/>
+      <c r="H84" s="33"/>
+      <c r="I84" s="33"/>
+    </row>
+    <row r="85" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B85" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="D85" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="26">
         <v>1</v>
       </c>
-      <c r="F74" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="G74" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="H74" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="I74" s="24" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="70"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="26">
+      <c r="F85" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G85" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="H85" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="I85" s="24" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="72"/>
+      <c r="B86" s="70"/>
+      <c r="C86" s="69"/>
+      <c r="D86" s="69"/>
+      <c r="E86" s="26">
         <v>2</v>
       </c>
-      <c r="F75" s="24" t="s">
+      <c r="F86" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="G75" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="H75" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="I75" s="24" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="70"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="67"/>
-      <c r="D76" s="67"/>
-      <c r="E76" s="26">
+      <c r="G86" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H86" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="I86" s="24" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="72"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="26">
         <v>3</v>
       </c>
-      <c r="F76" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="G76" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="H76" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="I76" s="24" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="71"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="67"/>
-      <c r="D77" s="67"/>
-      <c r="E77" s="26">
+      <c r="F87" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G87" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="H87" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="I87" s="24" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="73"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="69"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="26">
         <v>4</v>
       </c>
-      <c r="F77" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="G77" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="H77" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="I77" s="24" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="32"/>
-      <c r="B78" s="64" t="s">
-        <v>346</v>
-      </c>
-      <c r="C78" s="65"/>
-      <c r="D78" s="66"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="33"/>
-    </row>
-    <row r="79" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="B79" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="C79" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="E79" s="26">
-        <v>1</v>
-      </c>
-      <c r="F79" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G79" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="H79" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="I79" s="24" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="70"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="26">
-        <v>2</v>
-      </c>
-      <c r="F80" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="G80" s="24" t="s">
+      <c r="F88" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="G88" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="H80" s="24" t="s">
+      <c r="H88" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="I80" s="24" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="70"/>
-      <c r="B81" s="68"/>
-      <c r="C81" s="67"/>
-      <c r="D81" s="67"/>
-      <c r="E81" s="26">
-        <v>3</v>
-      </c>
-      <c r="F81" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="G81" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="H81" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="I81" s="24" t="s">
+      <c r="I88" s="24" t="s">
         <v>327</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="71"/>
-      <c r="B82" s="68"/>
-      <c r="C82" s="67"/>
-      <c r="D82" s="67"/>
-      <c r="E82" s="26">
-        <v>4</v>
-      </c>
-      <c r="F82" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="G82" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="H82" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="I82" s="24" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="32"/>
-      <c r="B83" s="64" t="s">
-        <v>347</v>
-      </c>
-      <c r="C83" s="65"/>
-      <c r="D83" s="66"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="33"/>
-      <c r="I83" s="33"/>
-    </row>
-    <row r="84" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="B84" s="68" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="D84" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="E84" s="26">
-        <v>1</v>
-      </c>
-      <c r="F84" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G84" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="H84" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="I84" s="24" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="70"/>
-      <c r="B85" s="68"/>
-      <c r="C85" s="67"/>
-      <c r="D85" s="67"/>
-      <c r="E85" s="26">
-        <v>2</v>
-      </c>
-      <c r="F85" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="G85" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="H85" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="I85" s="24" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="70"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="26">
-        <v>3</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="G86" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="H86" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="I86" s="24" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="71"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="67"/>
-      <c r="D87" s="67"/>
-      <c r="E87" s="26">
-        <v>4</v>
-      </c>
-      <c r="F87" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="G87" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="H87" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="I87" s="24" t="s">
-        <v>332</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="A34:A38"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="A4:A7"/>
@@ -4502,76 +4589,73 @@
     <mergeCell ref="C4:C7"/>
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A17:A22"/>
     <mergeCell ref="A24:A27"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
     <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B50:B53"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="C17:C22"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="D17:D22"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C79:C82"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="D49:D52"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D59:D62"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="A69:A72"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="D69:D72"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B79:B82"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="B69:B72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="D79:D82"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="C50:C53"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="D65:D68"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="C85:C88"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="D9:D15"/>
@@ -4583,7 +4667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E9DDE2-59FE-48B0-912A-9F161DB7D708}">
   <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="45.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4601,18 +4685,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="87" t="s">
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="89"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="94"/>
     </row>
     <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -4645,11 +4729,11 @@
     </row>
     <row r="3" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -4657,60 +4741,60 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="78" t="s">
-        <v>468</v>
-      </c>
-      <c r="C4" s="78" t="s">
-        <v>469</v>
-      </c>
-      <c r="D4" s="78" t="s">
-        <v>470</v>
+      <c r="B4" s="83" t="s">
+        <v>462</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>463</v>
+      </c>
+      <c r="D4" s="83" t="s">
+        <v>464</v>
       </c>
       <c r="E4" s="40">
         <v>1</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
       <c r="E5" s="40">
         <v>2</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="A6" s="77"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
       <c r="E6" s="40">
         <v>3</v>
       </c>
@@ -4720,10 +4804,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="40">
         <v>4</v>
       </c>
@@ -4734,11 +4818,11 @@
     </row>
     <row r="8" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
-      <c r="B8" s="92" t="s">
-        <v>333</v>
-      </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="94"/>
+      <c r="B8" s="97" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="98"/>
+      <c r="D8" s="99"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -4746,60 +4830,60 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="78" t="s">
-        <v>471</v>
-      </c>
-      <c r="C9" s="78" t="s">
-        <v>472</v>
-      </c>
-      <c r="D9" s="78" t="s">
-        <v>473</v>
+      <c r="B9" s="83" t="s">
+        <v>465</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>466</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>467</v>
       </c>
       <c r="E9" s="40">
         <v>1</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
+      <c r="A10" s="77"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
       <c r="E10" s="34">
         <v>2</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
       <c r="E11" s="40">
         <v>3</v>
       </c>
@@ -4809,10 +4893,10 @@
       <c r="I11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="40">
         <v>4</v>
       </c>
@@ -4823,11 +4907,11 @@
     </row>
     <row r="13" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35"/>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
       <c r="E13" s="35"/>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
@@ -4835,81 +4919,81 @@
       <c r="I13" s="36"/>
     </row>
     <row r="14" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="78" t="s">
-        <v>474</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>475</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>476</v>
+      <c r="B14" s="83" t="s">
+        <v>468</v>
+      </c>
+      <c r="C14" s="83" t="s">
+        <v>469</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>470</v>
       </c>
       <c r="E14" s="40">
         <v>1</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
       <c r="E15" s="40">
         <v>2</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="72"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
       <c r="E16" s="40">
         <v>3</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="72"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
+      <c r="A17" s="77"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="40">
         <v>4</v>
       </c>
@@ -4920,11 +5004,11 @@
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
-      <c r="B18" s="91" t="s">
+      <c r="B18" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="35"/>
       <c r="F18" s="36"/>
       <c r="G18" s="36"/>
@@ -4932,81 +5016,81 @@
       <c r="I18" s="36"/>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="78" t="s">
-        <v>474</v>
-      </c>
-      <c r="C19" s="78" t="s">
-        <v>477</v>
-      </c>
-      <c r="D19" s="78" t="s">
-        <v>478</v>
+      <c r="B19" s="83" t="s">
+        <v>468</v>
+      </c>
+      <c r="C19" s="83" t="s">
+        <v>471</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>472</v>
       </c>
       <c r="E19" s="40">
         <v>1</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="H19" s="41" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
       <c r="E20" s="40">
         <v>2</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G20" s="41" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="84"/>
       <c r="E21" s="40">
         <v>3</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
+      <c r="A22" s="77"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
       <c r="E22" s="40">
         <v>4</v>
       </c>
@@ -5017,11 +5101,11 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="96"/>
       <c r="E23" s="35"/>
       <c r="F23" s="36"/>
       <c r="G23" s="36"/>
@@ -5029,137 +5113,137 @@
       <c r="I23" s="36"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="75" t="s">
-        <v>479</v>
-      </c>
-      <c r="C24" s="75" t="s">
-        <v>480</v>
-      </c>
-      <c r="D24" s="75" t="s">
-        <v>481</v>
+      <c r="B24" s="80" t="s">
+        <v>473</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>474</v>
+      </c>
+      <c r="D24" s="80" t="s">
+        <v>475</v>
       </c>
       <c r="E24" s="40">
         <v>1</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="G24" s="41" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="H24" s="41" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="I24" s="41" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="76"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="40">
         <v>2</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="G25" s="41" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="I25" s="41" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="76"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
       <c r="E26" s="40">
         <v>3</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="76"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
       <c r="E27" s="40">
         <v>4</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="I27" s="41" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="76"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
       <c r="E28" s="40">
         <v>5</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
       <c r="E29" s="40">
         <v>6</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -5197,7 +5281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BBA4C7C-1B75-4CC3-9108-DB4740564B4D}">
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5222,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -5248,10 +5332,10 @@
     </row>
     <row r="2" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>7</v>
@@ -5272,7 +5356,7 @@
         <v>31</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J2" s="39" t="s">
         <v>36</v>
@@ -5280,19 +5364,19 @@
     </row>
     <row r="3" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F3" s="54" t="s">
         <v>27</v>
@@ -5301,10 +5385,10 @@
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J3" s="39" t="s">
         <v>39</v>
@@ -5312,10 +5396,10 @@
     </row>
     <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>8</v>
@@ -5336,7 +5420,7 @@
         <v>32</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J4" s="39" t="s">
         <v>38</v>
@@ -5344,10 +5428,10 @@
     </row>
     <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C5" s="54" t="s">
         <v>9</v>
@@ -5359,7 +5443,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>29</v>
+        <v>565</v>
       </c>
       <c r="G5" s="53" t="s">
         <v>30</v>
@@ -5368,7 +5452,7 @@
         <v>33</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J5" s="39" t="s">
         <v>40</v>
@@ -5376,179 +5460,179 @@
     </row>
     <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C6" s="52" t="s">
+        <v>369</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>374</v>
       </c>
-      <c r="D6" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>379</v>
-      </c>
       <c r="F6" s="54" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="39" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J6" s="39" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C7" s="52" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="E7" s="39" t="s">
         <v>375</v>
       </c>
-      <c r="D7" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>380</v>
-      </c>
       <c r="F7" s="54" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="39" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B8" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>406</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="E8" s="39" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>381</v>
-      </c>
       <c r="F8" s="54" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="39" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C9" s="52" t="s">
+        <v>372</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="E9" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>382</v>
-      </c>
       <c r="F9" s="54" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="39" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="J9" s="52" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F10" s="54" t="s">
+        <v>389</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>394</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>399</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="39" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J11" s="52" t="s">
         <v>67</v>
@@ -5556,29 +5640,29 @@
     </row>
     <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F12" s="54" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J12" s="52" t="s">
         <v>98</v>
@@ -5586,29 +5670,29 @@
     </row>
     <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G13" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J13" s="52" t="s">
         <v>102</v>
@@ -5616,29 +5700,29 @@
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F14" s="54" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J14" s="52" t="s">
         <v>106</v>
@@ -5646,29 +5730,29 @@
     </row>
     <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F15" s="54" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G15" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J15" s="52" t="s">
         <v>109</v>
@@ -5681,60 +5765,61 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E916DD94-D1B0-4F5A-A52B-CD3DDE50A874}">
-  <dimension ref="A1:AA60"/>
+  <dimension ref="A1:AE60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="45.28515625" customWidth="1"/>
     <col min="3" max="3" width="62.5703125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" customWidth="1"/>
-    <col min="6" max="7" width="5.42578125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="2" style="13" customWidth="1"/>
-    <col min="9" max="10" width="5.42578125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="2" style="13" customWidth="1"/>
-    <col min="12" max="13" width="5.42578125" style="13" customWidth="1"/>
-    <col min="14" max="14" width="2" style="13" customWidth="1"/>
-    <col min="15" max="16" width="5.42578125" style="13" customWidth="1"/>
-    <col min="17" max="17" width="2" style="13" customWidth="1"/>
-    <col min="18" max="19" width="5.42578125" style="13" customWidth="1"/>
-    <col min="20" max="20" width="2" style="13" customWidth="1"/>
-    <col min="21" max="22" width="5.42578125" style="13" customWidth="1"/>
-    <col min="23" max="23" width="2" style="13" customWidth="1"/>
-    <col min="24" max="27" width="5.42578125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="10" style="6" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="5.42578125" style="13" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="2" style="13" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="5.42578125" style="13" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="2" style="13" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="5.42578125" style="13" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="2" style="13" hidden="1" customWidth="1"/>
+    <col min="16" max="17" width="5.42578125" style="13" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="2" style="13" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="5.42578125" style="13" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="2" style="13" hidden="1" customWidth="1"/>
+    <col min="22" max="23" width="5.42578125" style="13" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="2" style="13" hidden="1" customWidth="1"/>
+    <col min="25" max="28" width="5.42578125" style="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F1" s="95" t="s">
+    <row r="1" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="96"/>
-      <c r="I1" s="95" t="s">
+      <c r="H1" s="101"/>
+      <c r="J1" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="K1" s="101"/>
+      <c r="M1" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="N1" s="101"/>
+      <c r="P1" s="100" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q1" s="101"/>
+      <c r="S1" s="100" t="s">
+        <v>349</v>
+      </c>
+      <c r="T1" s="101"/>
+      <c r="V1" s="100" t="s">
+        <v>350</v>
+      </c>
+      <c r="W1" s="101"/>
+      <c r="Y1" s="100" t="s">
         <v>351</v>
       </c>
-      <c r="J1" s="96"/>
-      <c r="L1" s="95" t="s">
-        <v>352</v>
-      </c>
-      <c r="M1" s="96"/>
-      <c r="O1" s="95" t="s">
-        <v>353</v>
-      </c>
-      <c r="P1" s="96"/>
-      <c r="R1" s="95" t="s">
-        <v>354</v>
-      </c>
-      <c r="S1" s="96"/>
-      <c r="U1" s="95" t="s">
-        <v>355</v>
-      </c>
-      <c r="V1" s="96"/>
-      <c r="X1" s="95" t="s">
-        <v>356</v>
-      </c>
-      <c r="Y1" s="96"/>
-    </row>
-    <row r="2" spans="1:27" s="17" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z1" s="101"/>
+    </row>
+    <row r="2" spans="1:31" s="17" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
@@ -5744,70 +5829,73 @@
       <c r="C2" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="12"/>
+      <c r="M2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="Q2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="12"/>
+      <c r="S2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="T2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="12"/>
+      <c r="V2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AA2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AB2" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>7</v>
@@ -5815,395 +5903,420 @@
       <c r="C3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>2</v>
       </c>
-      <c r="F3" s="14">
+      <c r="G3" s="14">
         <v>2</v>
       </c>
-      <c r="G3" s="14">
-        <f>E3-F3</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14">
-        <f t="shared" ref="J3:J18" si="0">G3-I3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14">
-        <f t="shared" ref="M3:M18" si="1">J3-L3</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14">
-        <f t="shared" ref="P3:P18" si="2">M3-O3</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14">
-        <f t="shared" ref="S3:S18" si="3">P3-R3</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14">
-        <f t="shared" ref="V3:V18" si="4">S3-U3</f>
-        <v>0</v>
-      </c>
-      <c r="W3" s="15"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14">
-        <f t="shared" ref="Y3:Y18" si="5">V3-X3</f>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="16">
-        <f>F3+I3+L3+O3+R3+U3+X3</f>
+      <c r="H3" s="14">
+        <f>F3-G3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14">
+        <f t="shared" ref="K3:K18" si="0">H3-J3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14">
+        <f t="shared" ref="N3:N18" si="1">K3-M3</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="15"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14">
+        <f t="shared" ref="Q3:Q18" si="2">N3-P3</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="15"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14">
+        <f t="shared" ref="T3:T18" si="3">Q3-S3</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="15"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14">
+        <f t="shared" ref="W3:W18" si="4">T3-V3</f>
+        <v>0</v>
+      </c>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14">
+        <f t="shared" ref="Z3:Z18" si="5">W3-Y3</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="16">
+        <f>G3+J3+M3+P3+S3+V3+Y3</f>
         <v>2</v>
       </c>
-      <c r="AA3" s="16">
-        <f t="shared" ref="AA3:AA16" si="6">E3-Z3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB3" s="16">
+        <f t="shared" ref="AB3:AB16" si="6">F3-AA3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="57"/>
       <c r="C4" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="F4" s="14">
+      <c r="G4" s="14">
         <v>2</v>
       </c>
-      <c r="G4" s="14">
-        <f t="shared" ref="G4:G60" si="7">E4-F4</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14">
+      <c r="H4" s="14">
+        <f t="shared" ref="H4:H60" si="7">F4-G4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14">
+      <c r="L4" s="15"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14">
+      <c r="O4" s="15"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14">
+      <c r="R4" s="15"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T4" s="15"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14">
+      <c r="U4" s="15"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W4" s="15"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14">
+      <c r="X4" s="15"/>
+      <c r="Y4" s="14"/>
+      <c r="Z4" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z4" s="16">
-        <f t="shared" ref="Z4:Z22" si="8">F4+I4+L4+O4+R4+U4+X4</f>
+      <c r="AA4" s="16">
+        <f t="shared" ref="AA4:AA22" si="8">G4+J4+M4+P4+S4+V4+Y4</f>
         <v>2</v>
       </c>
-      <c r="AA4" s="16">
+      <c r="AB4" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="57"/>
       <c r="C5" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="14">
+      <c r="G5" s="14">
         <v>2</v>
       </c>
-      <c r="G5" s="14">
+      <c r="H5" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14">
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14">
+      <c r="L5" s="15"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14">
+      <c r="O5" s="15"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14">
+      <c r="R5" s="15"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14">
+      <c r="U5" s="15"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W5" s="15"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14">
+      <c r="X5" s="15"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z5" s="16">
+      <c r="AA5" s="16">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AA5" s="16">
+      <c r="AB5" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="57"/>
       <c r="C6" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>3</v>
       </c>
-      <c r="F6" s="14">
+      <c r="G6" s="14">
         <v>3</v>
       </c>
-      <c r="G6" s="14">
+      <c r="H6" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14">
+      <c r="I6" s="15"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14">
+      <c r="L6" s="15"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14">
+      <c r="O6" s="15"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14">
+      <c r="R6" s="15"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T6" s="15"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14">
+      <c r="U6" s="15"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W6" s="15"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14">
+      <c r="X6" s="15"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="16">
+      <c r="AA6" s="16">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AA6" s="16">
+      <c r="AB6" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE6" s="107"/>
+    </row>
+    <row r="7" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="D7" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="14"/>
+      <c r="F7" s="2"/>
       <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
       <c r="J7" s="14"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
       <c r="M7" s="14"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="15"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="15"/>
       <c r="S7" s="14"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="15"/>
       <c r="V7" s="14"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="15"/>
       <c r="Y7" s="14"/>
-      <c r="Z7" s="16"/>
+      <c r="Z7" s="14"/>
       <c r="AA7" s="16"/>
-    </row>
-    <row r="8" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB7" s="16"/>
+    </row>
+    <row r="8" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="57"/>
       <c r="C8" s="50" t="s">
-        <v>366</v>
-      </c>
-      <c r="D8" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="14"/>
+      <c r="F8" s="2"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
       <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="14"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="15"/>
       <c r="P8" s="14"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="15"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="15"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="15"/>
       <c r="Y8" s="14"/>
-      <c r="Z8" s="16"/>
+      <c r="Z8" s="14"/>
       <c r="AA8" s="16"/>
-    </row>
-    <row r="9" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB8" s="16"/>
+    </row>
+    <row r="9" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="57"/>
       <c r="C9" s="50" t="s">
-        <v>367</v>
-      </c>
-      <c r="D9" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="14"/>
+      <c r="F9" s="2"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="15"/>
       <c r="M9" s="14"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
       <c r="P9" s="14"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="15"/>
       <c r="S9" s="14"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="15"/>
       <c r="V9" s="14"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="15"/>
       <c r="Y9" s="14"/>
-      <c r="Z9" s="16"/>
+      <c r="Z9" s="14"/>
       <c r="AA9" s="16"/>
-    </row>
-    <row r="10" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB9" s="16"/>
+    </row>
+    <row r="10" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="57"/>
       <c r="C10" s="50" t="s">
-        <v>368</v>
-      </c>
-      <c r="D10" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="14"/>
+      <c r="F10" s="2"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="15"/>
       <c r="M10" s="14"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="15"/>
       <c r="P10" s="14"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="15"/>
       <c r="S10" s="14"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="15"/>
       <c r="V10" s="14"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="15"/>
       <c r="Y10" s="14"/>
-      <c r="Z10" s="16"/>
+      <c r="Z10" s="14"/>
       <c r="AA10" s="16"/>
-    </row>
-    <row r="11" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB10" s="16"/>
+    </row>
+    <row r="11" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B11" s="56" t="s">
         <v>8</v>
@@ -6211,243 +6324,255 @@
       <c r="C11" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14">
+      <c r="F11" s="2"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14">
+      <c r="I11" s="15"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14">
+      <c r="L11" s="15"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14">
+      <c r="O11" s="15"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14">
+      <c r="R11" s="15"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T11" s="15"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14">
+      <c r="U11" s="15"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W11" s="15"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14">
+      <c r="X11" s="15"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="16">
+      <c r="AA11" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="16">
+      <c r="AB11" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="57"/>
       <c r="C12" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14">
+      <c r="F12" s="2"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14">
+      <c r="I12" s="15"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14">
+      <c r="L12" s="15"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="15"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14">
+      <c r="O12" s="15"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14">
+      <c r="R12" s="15"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T12" s="15"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14">
+      <c r="U12" s="15"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W12" s="15"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14">
+      <c r="X12" s="15"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="16">
+      <c r="AA12" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="16">
+      <c r="AB12" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="57"/>
       <c r="C13" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14">
+      <c r="F13" s="2"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14">
+      <c r="I13" s="15"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14">
+      <c r="L13" s="15"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14">
+      <c r="O13" s="15"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14">
+      <c r="R13" s="15"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T13" s="15"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14">
+      <c r="U13" s="15"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W13" s="15"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14">
+      <c r="X13" s="15"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="16">
+      <c r="AA13" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="16">
+      <c r="AB13" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="57"/>
       <c r="C14" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14">
+      <c r="F14" s="2"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14">
+      <c r="I14" s="15"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14">
+      <c r="L14" s="15"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14">
+      <c r="O14" s="15"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14">
+      <c r="R14" s="15"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T14" s="15"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14">
+      <c r="U14" s="15"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W14" s="15"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14">
+      <c r="X14" s="15"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="16">
+      <c r="AA14" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="16">
+      <c r="AB14" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B15" s="56" t="s">
         <v>9</v>
@@ -6455,2005 +6580,2144 @@
       <c r="C15" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14">
+      <c r="F15" s="2"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14">
+      <c r="I15" s="15"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14">
+      <c r="L15" s="15"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="15"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14">
+      <c r="O15" s="15"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14">
+      <c r="R15" s="15"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T15" s="15"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14">
+      <c r="U15" s="15"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W15" s="15"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14">
+      <c r="X15" s="15"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="16">
+      <c r="AA15" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="16">
+      <c r="AB15" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="57"/>
       <c r="C16" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14">
+      <c r="F16" s="2"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14">
+      <c r="I16" s="15"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14">
+      <c r="L16" s="15"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14">
+      <c r="O16" s="15"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14">
+      <c r="R16" s="15"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T16" s="15"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14">
+      <c r="U16" s="15"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W16" s="15"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14">
+      <c r="X16" s="15"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="16">
+      <c r="AA16" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="16">
+      <c r="AB16" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="57"/>
       <c r="C17" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14">
+      <c r="F17" s="2"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14">
+      <c r="I17" s="15"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14">
+      <c r="L17" s="15"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="15"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14">
+      <c r="O17" s="15"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14">
+      <c r="R17" s="15"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T17" s="15"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14">
+      <c r="U17" s="15"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W17" s="15"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14">
+      <c r="X17" s="15"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="16">
+      <c r="AA17" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="16">
-        <f t="shared" ref="AA17:AA22" si="9">E17-Z17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB17" s="16">
+        <f t="shared" ref="AB17:AB22" si="9">F17-AA17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="57"/>
       <c r="C18" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14">
+      <c r="F18" s="2"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14">
+      <c r="I18" s="15"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14">
+      <c r="L18" s="15"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="15"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14">
+      <c r="O18" s="15"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14">
+      <c r="R18" s="15"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T18" s="15"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14">
+      <c r="U18" s="15"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W18" s="15"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14">
+      <c r="X18" s="15"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="16">
+      <c r="AA18" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="16">
+      <c r="AB18" s="16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="58"/>
       <c r="C19" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="54" t="s">
+        <v>385</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="14">
+      <c r="F19" s="4"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="38"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="38"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="15"/>
       <c r="M19" s="38"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="15"/>
       <c r="P19" s="38"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="15"/>
       <c r="S19" s="38"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="15"/>
       <c r="V19" s="38"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="15"/>
       <c r="Y19" s="38"/>
-      <c r="Z19" s="16">
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="16">
+      <c r="AB19" s="16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="58"/>
       <c r="C20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="54" t="s">
+        <v>385</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="14">
+      <c r="F20" s="4"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="38"/>
+      <c r="I20" s="15"/>
       <c r="J20" s="38"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="15"/>
       <c r="M20" s="38"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="15"/>
       <c r="P20" s="38"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="15"/>
       <c r="S20" s="38"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="15"/>
       <c r="V20" s="38"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="15"/>
       <c r="Y20" s="38"/>
-      <c r="Z20" s="16">
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="16">
+      <c r="AB20" s="16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="58"/>
       <c r="C21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="54" t="s">
+        <v>385</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="14">
+      <c r="F21" s="4"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="38"/>
+      <c r="I21" s="15"/>
       <c r="J21" s="38"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="15"/>
       <c r="M21" s="38"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="15"/>
       <c r="P21" s="38"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="15"/>
       <c r="S21" s="38"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="15"/>
       <c r="V21" s="38"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="15"/>
       <c r="Y21" s="38"/>
-      <c r="Z21" s="16">
+      <c r="Z21" s="38"/>
+      <c r="AA21" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="16">
+      <c r="AB21" s="16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="58"/>
       <c r="C22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="54" t="s">
+        <v>385</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="14">
+      <c r="F22" s="4"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="38"/>
+      <c r="I22" s="15"/>
       <c r="J22" s="38"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="15"/>
       <c r="M22" s="38"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="15"/>
       <c r="P22" s="38"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="15"/>
       <c r="S22" s="38"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="15"/>
       <c r="V22" s="38"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="38"/>
+      <c r="W22" s="38"/>
+      <c r="X22" s="15"/>
       <c r="Y22" s="38"/>
-      <c r="Z22" s="16">
+      <c r="Z22" s="38"/>
+      <c r="AA22" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA22" s="16">
+      <c r="AB22" s="16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="14">
+        <v>417</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="38"/>
+      <c r="I23" s="15"/>
       <c r="J23" s="38"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="15"/>
       <c r="M23" s="38"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="15"/>
       <c r="P23" s="38"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="15"/>
       <c r="S23" s="38"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="15"/>
       <c r="V23" s="38"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="15"/>
       <c r="Y23" s="38"/>
-      <c r="Z23" s="16">
-        <f t="shared" ref="Z23:Z36" si="10">F23+I23+L23+O23+R23+U23+X23</f>
-        <v>0</v>
-      </c>
+      <c r="Z23" s="38"/>
       <c r="AA23" s="16">
-        <f t="shared" ref="AA23:AA36" si="11">E23-Z23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA23:AA36" si="10">G23+J23+M23+P23+S23+V23+Y23</f>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="16">
+        <f t="shared" ref="AB23:AB36" si="11">F23-AA23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="58"/>
       <c r="C24" s="52" t="s">
-        <v>423</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="14">
+        <v>418</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="38"/>
+      <c r="I24" s="15"/>
       <c r="J24" s="38"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="15"/>
       <c r="M24" s="38"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="15"/>
       <c r="P24" s="38"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="15"/>
       <c r="S24" s="38"/>
-      <c r="T24" s="15"/>
-      <c r="U24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="15"/>
       <c r="V24" s="38"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="38"/>
+      <c r="W24" s="38"/>
+      <c r="X24" s="15"/>
       <c r="Y24" s="38"/>
-      <c r="Z24" s="16"/>
+      <c r="Z24" s="38"/>
       <c r="AA24" s="16"/>
-    </row>
-    <row r="25" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB24" s="16"/>
+    </row>
+    <row r="25" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="58"/>
       <c r="C25" s="52" t="s">
-        <v>424</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="14">
+        <v>419</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="38"/>
+      <c r="I25" s="15"/>
       <c r="J25" s="38"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="15"/>
       <c r="M25" s="38"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="15"/>
       <c r="P25" s="38"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="15"/>
       <c r="S25" s="38"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="38"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="15"/>
       <c r="V25" s="38"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="38"/>
+      <c r="W25" s="38"/>
+      <c r="X25" s="15"/>
       <c r="Y25" s="38"/>
-      <c r="Z25" s="16"/>
+      <c r="Z25" s="38"/>
       <c r="AA25" s="16"/>
-    </row>
-    <row r="26" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB25" s="16"/>
+    </row>
+    <row r="26" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="58"/>
       <c r="C26" s="52" t="s">
-        <v>463</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="14">
+        <v>564</v>
+      </c>
+      <c r="D26" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="38"/>
+      <c r="I26" s="15"/>
       <c r="J26" s="38"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="15"/>
       <c r="M26" s="38"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="15"/>
       <c r="P26" s="38"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="15"/>
       <c r="S26" s="38"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="15"/>
       <c r="V26" s="38"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="15"/>
       <c r="Y26" s="38"/>
-      <c r="Z26" s="16"/>
+      <c r="Z26" s="38"/>
       <c r="AA26" s="16"/>
-    </row>
-    <row r="27" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB26" s="16"/>
+    </row>
+    <row r="27" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="58"/>
       <c r="C27" s="52" t="s">
-        <v>464</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="14">
+        <v>458</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H27" s="15"/>
-      <c r="I27" s="38"/>
+      <c r="I27" s="15"/>
       <c r="J27" s="38"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="15"/>
       <c r="M27" s="38"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="15"/>
       <c r="P27" s="38"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="15"/>
       <c r="S27" s="38"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="38"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="15"/>
       <c r="V27" s="38"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="38"/>
+      <c r="W27" s="38"/>
+      <c r="X27" s="15"/>
       <c r="Y27" s="38"/>
-      <c r="Z27" s="16"/>
+      <c r="Z27" s="38"/>
       <c r="AA27" s="16"/>
-    </row>
-    <row r="28" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB27" s="16"/>
+    </row>
+    <row r="28" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="58"/>
       <c r="C28" s="52" t="s">
-        <v>465</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="14">
+        <v>459</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="38"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="38"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="15"/>
       <c r="M28" s="38"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="15"/>
       <c r="P28" s="38"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="15"/>
       <c r="S28" s="38"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="15"/>
       <c r="V28" s="38"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="15"/>
       <c r="Y28" s="38"/>
-      <c r="Z28" s="16"/>
+      <c r="Z28" s="38"/>
       <c r="AA28" s="16"/>
-    </row>
-    <row r="29" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB28" s="16"/>
+    </row>
+    <row r="29" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="58"/>
       <c r="C29" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="14">
+        <v>418</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H29" s="15"/>
-      <c r="I29" s="38"/>
+      <c r="I29" s="15"/>
       <c r="J29" s="38"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="15"/>
       <c r="M29" s="38"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="15"/>
       <c r="P29" s="38"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="15"/>
       <c r="S29" s="38"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="15"/>
       <c r="V29" s="38"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="38"/>
+      <c r="W29" s="38"/>
+      <c r="X29" s="15"/>
       <c r="Y29" s="38"/>
-      <c r="Z29" s="16">
+      <c r="Z29" s="38"/>
+      <c r="AA29" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="16">
+      <c r="AB29" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="58"/>
       <c r="C30" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="14">
+        <v>419</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>386</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H30" s="15"/>
-      <c r="I30" s="38"/>
+      <c r="I30" s="15"/>
       <c r="J30" s="38"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="15"/>
       <c r="M30" s="38"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="15"/>
       <c r="P30" s="38"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="15"/>
       <c r="S30" s="38"/>
-      <c r="T30" s="15"/>
-      <c r="U30" s="38"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="15"/>
       <c r="V30" s="38"/>
-      <c r="W30" s="15"/>
-      <c r="X30" s="38"/>
+      <c r="W30" s="38"/>
+      <c r="X30" s="15"/>
       <c r="Y30" s="38"/>
-      <c r="Z30" s="16">
+      <c r="Z30" s="38"/>
+      <c r="AA30" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="16">
+      <c r="AB30" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B31" s="58" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="14">
+        <v>420</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="38"/>
+      <c r="I31" s="15"/>
       <c r="J31" s="38"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="15"/>
       <c r="M31" s="38"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="15"/>
       <c r="P31" s="38"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="15"/>
       <c r="S31" s="38"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="15"/>
       <c r="V31" s="38"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="15"/>
       <c r="Y31" s="38"/>
-      <c r="Z31" s="16">
+      <c r="Z31" s="38"/>
+      <c r="AA31" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="16">
+      <c r="AB31" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="58"/>
       <c r="C32" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="14">
+        <v>421</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="38"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="38"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="15"/>
       <c r="M32" s="38"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="15"/>
       <c r="P32" s="38"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="15"/>
       <c r="S32" s="38"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="15"/>
       <c r="V32" s="38"/>
-      <c r="W32" s="15"/>
-      <c r="X32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="15"/>
       <c r="Y32" s="38"/>
-      <c r="Z32" s="16">
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="16">
+      <c r="AB32" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="58"/>
       <c r="C33" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="14">
+        <v>422</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H33" s="15"/>
-      <c r="I33" s="38"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="38"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="15"/>
       <c r="M33" s="38"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="15"/>
       <c r="P33" s="38"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="15"/>
       <c r="S33" s="38"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="38"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="15"/>
       <c r="V33" s="38"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="38"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="15"/>
       <c r="Y33" s="38"/>
-      <c r="Z33" s="16">
+      <c r="Z33" s="38"/>
+      <c r="AA33" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="16">
+      <c r="AB33" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="14">
+        <v>423</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="38"/>
+      <c r="I34" s="15"/>
       <c r="J34" s="38"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="15"/>
       <c r="M34" s="38"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="15"/>
       <c r="P34" s="38"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="15"/>
       <c r="S34" s="38"/>
-      <c r="T34" s="15"/>
-      <c r="U34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="15"/>
       <c r="V34" s="38"/>
-      <c r="W34" s="15"/>
-      <c r="X34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="15"/>
       <c r="Y34" s="38"/>
-      <c r="Z34" s="16">
+      <c r="Z34" s="38"/>
+      <c r="AA34" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="16">
+      <c r="AB34" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="58"/>
       <c r="C35" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="14">
+        <v>424</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E35" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="38"/>
+      <c r="I35" s="15"/>
       <c r="J35" s="38"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="15"/>
       <c r="M35" s="38"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="15"/>
       <c r="P35" s="38"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="15"/>
       <c r="S35" s="38"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="38"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="15"/>
       <c r="V35" s="38"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="38"/>
+      <c r="W35" s="38"/>
+      <c r="X35" s="15"/>
       <c r="Y35" s="38"/>
-      <c r="Z35" s="16">
+      <c r="Z35" s="38"/>
+      <c r="AA35" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA35" s="16">
+      <c r="AB35" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="58"/>
       <c r="C36" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="D36" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="14">
+        <v>425</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H36" s="15"/>
-      <c r="I36" s="38"/>
+      <c r="I36" s="15"/>
       <c r="J36" s="38"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="15"/>
       <c r="M36" s="38"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="15"/>
       <c r="P36" s="38"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="15"/>
       <c r="S36" s="38"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="15"/>
       <c r="V36" s="38"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="15"/>
       <c r="Y36" s="38"/>
-      <c r="Z36" s="16">
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="16">
+      <c r="AB36" s="16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B37" s="58" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="14">
+        <v>426</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>388</v>
+      </c>
+      <c r="E37" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="38"/>
+      <c r="I37" s="15"/>
       <c r="J37" s="38"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="15"/>
       <c r="M37" s="38"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="15"/>
       <c r="P37" s="38"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="15"/>
       <c r="S37" s="38"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="15"/>
       <c r="V37" s="38"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="38"/>
+      <c r="W37" s="38"/>
+      <c r="X37" s="15"/>
       <c r="Y37" s="38"/>
-      <c r="Z37" s="16">
-        <f t="shared" ref="Z37:Z60" si="12">F37+I37+L37+O37+R37+U37+X37</f>
-        <v>0</v>
-      </c>
+      <c r="Z37" s="38"/>
       <c r="AA37" s="16">
-        <f t="shared" ref="AA37:AA60" si="13">E37-Z37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA37:AA60" si="12">G37+J37+M37+P37+S37+V37+Y37</f>
+        <v>0</v>
+      </c>
+      <c r="AB37" s="16">
+        <f t="shared" ref="AB37:AB60" si="13">F37-AA37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="58"/>
       <c r="C38" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="14">
+        <v>427</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>388</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="38"/>
+      <c r="I38" s="15"/>
       <c r="J38" s="38"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="15"/>
       <c r="M38" s="38"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="15"/>
       <c r="P38" s="38"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="15"/>
       <c r="S38" s="38"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="15"/>
       <c r="V38" s="38"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="15"/>
       <c r="Y38" s="38"/>
-      <c r="Z38" s="16">
+      <c r="Z38" s="38"/>
+      <c r="AA38" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA38" s="16">
+      <c r="AB38" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="58"/>
       <c r="C39" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="14">
+        <v>428</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>388</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="38"/>
+      <c r="I39" s="15"/>
       <c r="J39" s="38"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="15"/>
       <c r="M39" s="38"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="15"/>
       <c r="P39" s="38"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="15"/>
       <c r="S39" s="38"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="15"/>
       <c r="V39" s="38"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="38"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="15"/>
       <c r="Y39" s="38"/>
-      <c r="Z39" s="16">
+      <c r="Z39" s="38"/>
+      <c r="AA39" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA39" s="16">
+      <c r="AB39" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="58"/>
       <c r="C40" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="14">
+        <v>429</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>388</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H40" s="15"/>
-      <c r="I40" s="38"/>
+      <c r="I40" s="15"/>
       <c r="J40" s="38"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="15"/>
       <c r="M40" s="38"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="38"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="15"/>
       <c r="P40" s="38"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40" s="15"/>
       <c r="S40" s="38"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="38"/>
+      <c r="T40" s="38"/>
+      <c r="U40" s="15"/>
       <c r="V40" s="38"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="38"/>
+      <c r="W40" s="38"/>
+      <c r="X40" s="15"/>
       <c r="Y40" s="38"/>
-      <c r="Z40" s="16">
+      <c r="Z40" s="38"/>
+      <c r="AA40" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA40" s="16">
+      <c r="AB40" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B41" s="58" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="14">
+        <v>430</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>389</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H41" s="15"/>
-      <c r="I41" s="38"/>
+      <c r="I41" s="15"/>
       <c r="J41" s="38"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="15"/>
       <c r="M41" s="38"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="15"/>
       <c r="P41" s="38"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="38"/>
+      <c r="Q41" s="38"/>
+      <c r="R41" s="15"/>
       <c r="S41" s="38"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="38"/>
+      <c r="T41" s="38"/>
+      <c r="U41" s="15"/>
       <c r="V41" s="38"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="38"/>
+      <c r="W41" s="38"/>
+      <c r="X41" s="15"/>
       <c r="Y41" s="38"/>
-      <c r="Z41" s="16">
+      <c r="Z41" s="38"/>
+      <c r="AA41" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA41" s="16">
+      <c r="AB41" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="58"/>
       <c r="C42" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="D42" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="14">
+        <v>431</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>389</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="38"/>
+      <c r="I42" s="15"/>
       <c r="J42" s="38"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="38"/>
+      <c r="K42" s="38"/>
+      <c r="L42" s="15"/>
       <c r="M42" s="38"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="15"/>
       <c r="P42" s="38"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="38"/>
+      <c r="Q42" s="38"/>
+      <c r="R42" s="15"/>
       <c r="S42" s="38"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="38"/>
+      <c r="T42" s="38"/>
+      <c r="U42" s="15"/>
       <c r="V42" s="38"/>
-      <c r="W42" s="15"/>
-      <c r="X42" s="38"/>
+      <c r="W42" s="38"/>
+      <c r="X42" s="15"/>
       <c r="Y42" s="38"/>
-      <c r="Z42" s="16">
+      <c r="Z42" s="38"/>
+      <c r="AA42" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="16">
+      <c r="AB42" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="58"/>
       <c r="C43" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="D43" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="14">
+        <v>432</v>
+      </c>
+      <c r="D43" s="54" t="s">
+        <v>389</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H43" s="15"/>
-      <c r="I43" s="38"/>
+      <c r="I43" s="15"/>
       <c r="J43" s="38"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="15"/>
       <c r="M43" s="38"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="15"/>
       <c r="P43" s="38"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="15"/>
       <c r="S43" s="38"/>
-      <c r="T43" s="15"/>
-      <c r="U43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="15"/>
       <c r="V43" s="38"/>
-      <c r="W43" s="15"/>
-      <c r="X43" s="38"/>
+      <c r="W43" s="38"/>
+      <c r="X43" s="15"/>
       <c r="Y43" s="38"/>
-      <c r="Z43" s="16">
+      <c r="Z43" s="38"/>
+      <c r="AA43" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA43" s="16">
+      <c r="AB43" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="D44" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="14">
+        <v>433</v>
+      </c>
+      <c r="D44" s="54" t="s">
+        <v>390</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H44" s="15"/>
-      <c r="I44" s="38"/>
+      <c r="I44" s="15"/>
       <c r="J44" s="38"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="15"/>
       <c r="M44" s="38"/>
-      <c r="N44" s="15"/>
-      <c r="O44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="15"/>
       <c r="P44" s="38"/>
-      <c r="Q44" s="15"/>
-      <c r="R44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="15"/>
       <c r="S44" s="38"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="38"/>
+      <c r="T44" s="38"/>
+      <c r="U44" s="15"/>
       <c r="V44" s="38"/>
-      <c r="W44" s="15"/>
-      <c r="X44" s="38"/>
+      <c r="W44" s="38"/>
+      <c r="X44" s="15"/>
       <c r="Y44" s="38"/>
-      <c r="Z44" s="16">
+      <c r="Z44" s="38"/>
+      <c r="AA44" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA44" s="16">
+      <c r="AB44" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="58"/>
       <c r="C45" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="D45" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="14">
+        <v>434</v>
+      </c>
+      <c r="D45" s="54" t="s">
+        <v>390</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="38"/>
+      <c r="I45" s="15"/>
       <c r="J45" s="38"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="15"/>
       <c r="M45" s="38"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="15"/>
       <c r="P45" s="38"/>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="38"/>
+      <c r="Q45" s="38"/>
+      <c r="R45" s="15"/>
       <c r="S45" s="38"/>
-      <c r="T45" s="15"/>
-      <c r="U45" s="38"/>
+      <c r="T45" s="38"/>
+      <c r="U45" s="15"/>
       <c r="V45" s="38"/>
-      <c r="W45" s="15"/>
-      <c r="X45" s="38"/>
+      <c r="W45" s="38"/>
+      <c r="X45" s="15"/>
       <c r="Y45" s="38"/>
-      <c r="Z45" s="16">
+      <c r="Z45" s="38"/>
+      <c r="AA45" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA45" s="16">
+      <c r="AB45" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="58"/>
       <c r="C46" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="D46" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="14">
+        <v>435</v>
+      </c>
+      <c r="D46" s="54" t="s">
+        <v>390</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="38"/>
+      <c r="I46" s="15"/>
       <c r="J46" s="38"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="38"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="15"/>
       <c r="M46" s="38"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="15"/>
       <c r="P46" s="38"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46" s="15"/>
       <c r="S46" s="38"/>
-      <c r="T46" s="15"/>
-      <c r="U46" s="38"/>
+      <c r="T46" s="38"/>
+      <c r="U46" s="15"/>
       <c r="V46" s="38"/>
-      <c r="W46" s="15"/>
-      <c r="X46" s="38"/>
+      <c r="W46" s="38"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="38"/>
-      <c r="Z46" s="16">
+      <c r="Z46" s="38"/>
+      <c r="AA46" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="16">
+      <c r="AB46" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B47" s="58" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="14">
+        <v>436</v>
+      </c>
+      <c r="D47" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H47" s="15"/>
-      <c r="I47" s="38"/>
+      <c r="I47" s="15"/>
       <c r="J47" s="38"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="38"/>
+      <c r="K47" s="38"/>
+      <c r="L47" s="15"/>
       <c r="M47" s="38"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="38"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="15"/>
       <c r="P47" s="38"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="38"/>
+      <c r="Q47" s="38"/>
+      <c r="R47" s="15"/>
       <c r="S47" s="38"/>
-      <c r="T47" s="15"/>
-      <c r="U47" s="38"/>
+      <c r="T47" s="38"/>
+      <c r="U47" s="15"/>
       <c r="V47" s="38"/>
-      <c r="W47" s="15"/>
-      <c r="X47" s="38"/>
+      <c r="W47" s="38"/>
+      <c r="X47" s="15"/>
       <c r="Y47" s="38"/>
-      <c r="Z47" s="16">
+      <c r="Z47" s="38"/>
+      <c r="AA47" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="16">
+      <c r="AB47" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="48"/>
       <c r="B48" s="58"/>
       <c r="C48" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="D48" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="14">
+        <v>460</v>
+      </c>
+      <c r="D48" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H48" s="15"/>
-      <c r="I48" s="38"/>
+      <c r="I48" s="15"/>
       <c r="J48" s="38"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="38"/>
+      <c r="K48" s="38"/>
+      <c r="L48" s="15"/>
       <c r="M48" s="38"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="38"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="15"/>
       <c r="P48" s="38"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="38"/>
+      <c r="Q48" s="38"/>
+      <c r="R48" s="15"/>
       <c r="S48" s="38"/>
-      <c r="T48" s="15"/>
-      <c r="U48" s="38"/>
+      <c r="T48" s="38"/>
+      <c r="U48" s="15"/>
       <c r="V48" s="38"/>
-      <c r="W48" s="15"/>
-      <c r="X48" s="38"/>
+      <c r="W48" s="38"/>
+      <c r="X48" s="15"/>
       <c r="Y48" s="38"/>
-      <c r="Z48" s="16"/>
+      <c r="Z48" s="38"/>
       <c r="AA48" s="16"/>
-    </row>
-    <row r="49" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB48" s="16"/>
+    </row>
+    <row r="49" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="58"/>
       <c r="C49" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="D49" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="14">
+        <v>437</v>
+      </c>
+      <c r="D49" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H49" s="15"/>
-      <c r="I49" s="38"/>
+      <c r="I49" s="15"/>
       <c r="J49" s="38"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="38"/>
+      <c r="K49" s="38"/>
+      <c r="L49" s="15"/>
       <c r="M49" s="38"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="38"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="15"/>
       <c r="P49" s="38"/>
-      <c r="Q49" s="15"/>
-      <c r="R49" s="38"/>
+      <c r="Q49" s="38"/>
+      <c r="R49" s="15"/>
       <c r="S49" s="38"/>
-      <c r="T49" s="15"/>
-      <c r="U49" s="38"/>
+      <c r="T49" s="38"/>
+      <c r="U49" s="15"/>
       <c r="V49" s="38"/>
-      <c r="W49" s="15"/>
-      <c r="X49" s="38"/>
+      <c r="W49" s="38"/>
+      <c r="X49" s="15"/>
       <c r="Y49" s="38"/>
-      <c r="Z49" s="16">
+      <c r="Z49" s="38"/>
+      <c r="AA49" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="16">
+      <c r="AB49" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="58"/>
       <c r="C50" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="D50" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="14">
+        <v>461</v>
+      </c>
+      <c r="D50" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H50" s="15"/>
-      <c r="I50" s="38"/>
+      <c r="I50" s="15"/>
       <c r="J50" s="38"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="15"/>
       <c r="M50" s="38"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="38"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="15"/>
       <c r="P50" s="38"/>
-      <c r="Q50" s="15"/>
-      <c r="R50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="15"/>
       <c r="S50" s="38"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="38"/>
+      <c r="T50" s="38"/>
+      <c r="U50" s="15"/>
       <c r="V50" s="38"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="38"/>
+      <c r="W50" s="38"/>
+      <c r="X50" s="15"/>
       <c r="Y50" s="38"/>
-      <c r="Z50" s="16"/>
+      <c r="Z50" s="38"/>
       <c r="AA50" s="16"/>
-    </row>
-    <row r="51" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB50" s="16"/>
+    </row>
+    <row r="51" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="58"/>
       <c r="C51" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="D51" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="14">
+        <v>438</v>
+      </c>
+      <c r="D51" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="E51" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H51" s="15"/>
-      <c r="I51" s="38"/>
+      <c r="I51" s="15"/>
       <c r="J51" s="38"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="38"/>
+      <c r="K51" s="38"/>
+      <c r="L51" s="15"/>
       <c r="M51" s="38"/>
-      <c r="N51" s="15"/>
-      <c r="O51" s="38"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="15"/>
       <c r="P51" s="38"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="38"/>
+      <c r="Q51" s="38"/>
+      <c r="R51" s="15"/>
       <c r="S51" s="38"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="38"/>
+      <c r="T51" s="38"/>
+      <c r="U51" s="15"/>
       <c r="V51" s="38"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="38"/>
+      <c r="W51" s="38"/>
+      <c r="X51" s="15"/>
       <c r="Y51" s="38"/>
-      <c r="Z51" s="16">
+      <c r="Z51" s="38"/>
+      <c r="AA51" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="16">
+      <c r="AB51" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="D52" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="14">
+        <v>439</v>
+      </c>
+      <c r="D52" s="54" t="s">
+        <v>392</v>
+      </c>
+      <c r="E52" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H52" s="15"/>
-      <c r="I52" s="38"/>
+      <c r="I52" s="15"/>
       <c r="J52" s="38"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="38"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="15"/>
       <c r="M52" s="38"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="38"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="15"/>
       <c r="P52" s="38"/>
-      <c r="Q52" s="15"/>
-      <c r="R52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52" s="15"/>
       <c r="S52" s="38"/>
-      <c r="T52" s="15"/>
-      <c r="U52" s="38"/>
+      <c r="T52" s="38"/>
+      <c r="U52" s="15"/>
       <c r="V52" s="38"/>
-      <c r="W52" s="15"/>
-      <c r="X52" s="38"/>
+      <c r="W52" s="38"/>
+      <c r="X52" s="15"/>
       <c r="Y52" s="38"/>
-      <c r="Z52" s="16">
+      <c r="Z52" s="38"/>
+      <c r="AA52" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA52" s="16">
+      <c r="AB52" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="58"/>
       <c r="C53" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="D53" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="14">
+        <v>440</v>
+      </c>
+      <c r="D53" s="54" t="s">
+        <v>392</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H53" s="15"/>
-      <c r="I53" s="38"/>
+      <c r="I53" s="15"/>
       <c r="J53" s="38"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="15"/>
       <c r="M53" s="38"/>
-      <c r="N53" s="15"/>
-      <c r="O53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="15"/>
       <c r="P53" s="38"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="15"/>
       <c r="S53" s="38"/>
-      <c r="T53" s="15"/>
-      <c r="U53" s="38"/>
+      <c r="T53" s="38"/>
+      <c r="U53" s="15"/>
       <c r="V53" s="38"/>
-      <c r="W53" s="15"/>
-      <c r="X53" s="38"/>
+      <c r="W53" s="38"/>
+      <c r="X53" s="15"/>
       <c r="Y53" s="38"/>
-      <c r="Z53" s="16">
+      <c r="Z53" s="38"/>
+      <c r="AA53" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA53" s="16">
+      <c r="AB53" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="58"/>
       <c r="C54" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="D54" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="14">
+        <v>441</v>
+      </c>
+      <c r="D54" s="54" t="s">
+        <v>392</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H54" s="15"/>
-      <c r="I54" s="38"/>
+      <c r="I54" s="15"/>
       <c r="J54" s="38"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="15"/>
       <c r="M54" s="38"/>
-      <c r="N54" s="15"/>
-      <c r="O54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="15"/>
       <c r="P54" s="38"/>
-      <c r="Q54" s="15"/>
-      <c r="R54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="15"/>
       <c r="S54" s="38"/>
-      <c r="T54" s="15"/>
-      <c r="U54" s="38"/>
+      <c r="T54" s="38"/>
+      <c r="U54" s="15"/>
       <c r="V54" s="38"/>
-      <c r="W54" s="15"/>
-      <c r="X54" s="38"/>
+      <c r="W54" s="38"/>
+      <c r="X54" s="15"/>
       <c r="Y54" s="38"/>
-      <c r="Z54" s="16">
+      <c r="Z54" s="38"/>
+      <c r="AA54" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="16">
+      <c r="AB54" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="14">
+        <v>442</v>
+      </c>
+      <c r="D55" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E55" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H55" s="15"/>
-      <c r="I55" s="38"/>
+      <c r="I55" s="15"/>
       <c r="J55" s="38"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="15"/>
       <c r="M55" s="38"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="15"/>
       <c r="P55" s="38"/>
-      <c r="Q55" s="15"/>
-      <c r="R55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="15"/>
       <c r="S55" s="38"/>
-      <c r="T55" s="15"/>
-      <c r="U55" s="38"/>
+      <c r="T55" s="38"/>
+      <c r="U55" s="15"/>
       <c r="V55" s="38"/>
-      <c r="W55" s="15"/>
-      <c r="X55" s="38"/>
+      <c r="W55" s="38"/>
+      <c r="X55" s="15"/>
       <c r="Y55" s="38"/>
-      <c r="Z55" s="16">
+      <c r="Z55" s="38"/>
+      <c r="AA55" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA55" s="16">
+      <c r="AB55" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="58"/>
       <c r="C56" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="14">
+        <v>443</v>
+      </c>
+      <c r="D56" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H56" s="15"/>
-      <c r="I56" s="38"/>
+      <c r="I56" s="15"/>
       <c r="J56" s="38"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="15"/>
       <c r="M56" s="38"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="38"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="15"/>
       <c r="P56" s="38"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="38"/>
+      <c r="Q56" s="38"/>
+      <c r="R56" s="15"/>
       <c r="S56" s="38"/>
-      <c r="T56" s="15"/>
-      <c r="U56" s="38"/>
+      <c r="T56" s="38"/>
+      <c r="U56" s="15"/>
       <c r="V56" s="38"/>
-      <c r="W56" s="15"/>
-      <c r="X56" s="38"/>
+      <c r="W56" s="38"/>
+      <c r="X56" s="15"/>
       <c r="Y56" s="38"/>
-      <c r="Z56" s="16">
+      <c r="Z56" s="38"/>
+      <c r="AA56" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA56" s="16">
+      <c r="AB56" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="58"/>
       <c r="C57" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="14">
+        <v>444</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E57" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H57" s="15"/>
-      <c r="I57" s="38"/>
+      <c r="I57" s="15"/>
       <c r="J57" s="38"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="15"/>
       <c r="M57" s="38"/>
-      <c r="N57" s="15"/>
-      <c r="O57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="15"/>
       <c r="P57" s="38"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="15"/>
       <c r="S57" s="38"/>
-      <c r="T57" s="15"/>
-      <c r="U57" s="38"/>
+      <c r="T57" s="38"/>
+      <c r="U57" s="15"/>
       <c r="V57" s="38"/>
-      <c r="W57" s="15"/>
-      <c r="X57" s="38"/>
+      <c r="W57" s="38"/>
+      <c r="X57" s="15"/>
       <c r="Y57" s="38"/>
-      <c r="Z57" s="16">
+      <c r="Z57" s="38"/>
+      <c r="AA57" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA57" s="16">
+      <c r="AB57" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="D58" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="14">
+        <v>445</v>
+      </c>
+      <c r="D58" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E58" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H58" s="15"/>
-      <c r="I58" s="38"/>
+      <c r="I58" s="15"/>
       <c r="J58" s="38"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="38"/>
+      <c r="K58" s="38"/>
+      <c r="L58" s="15"/>
       <c r="M58" s="38"/>
-      <c r="N58" s="15"/>
-      <c r="O58" s="38"/>
+      <c r="N58" s="38"/>
+      <c r="O58" s="15"/>
       <c r="P58" s="38"/>
-      <c r="Q58" s="15"/>
-      <c r="R58" s="38"/>
+      <c r="Q58" s="38"/>
+      <c r="R58" s="15"/>
       <c r="S58" s="38"/>
-      <c r="T58" s="15"/>
-      <c r="U58" s="38"/>
+      <c r="T58" s="38"/>
+      <c r="U58" s="15"/>
       <c r="V58" s="38"/>
-      <c r="W58" s="15"/>
-      <c r="X58" s="38"/>
+      <c r="W58" s="38"/>
+      <c r="X58" s="15"/>
       <c r="Y58" s="38"/>
-      <c r="Z58" s="16">
+      <c r="Z58" s="38"/>
+      <c r="AA58" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA58" s="16">
+      <c r="AB58" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="14">
+        <v>446</v>
+      </c>
+      <c r="D59" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E59" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H59" s="15"/>
-      <c r="I59" s="38"/>
+      <c r="I59" s="15"/>
       <c r="J59" s="38"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="38"/>
+      <c r="K59" s="38"/>
+      <c r="L59" s="15"/>
       <c r="M59" s="38"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="38"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="15"/>
       <c r="P59" s="38"/>
-      <c r="Q59" s="15"/>
-      <c r="R59" s="38"/>
+      <c r="Q59" s="38"/>
+      <c r="R59" s="15"/>
       <c r="S59" s="38"/>
-      <c r="T59" s="15"/>
-      <c r="U59" s="38"/>
+      <c r="T59" s="38"/>
+      <c r="U59" s="15"/>
       <c r="V59" s="38"/>
-      <c r="W59" s="15"/>
-      <c r="X59" s="38"/>
+      <c r="W59" s="38"/>
+      <c r="X59" s="15"/>
       <c r="Y59" s="38"/>
-      <c r="Z59" s="16">
+      <c r="Z59" s="38"/>
+      <c r="AA59" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="16">
+      <c r="AB59" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="D60" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="E60" s="4"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="14">
+        <v>447</v>
+      </c>
+      <c r="D60" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E60" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H60" s="15"/>
-      <c r="I60" s="38"/>
+      <c r="I60" s="15"/>
       <c r="J60" s="38"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="38"/>
+      <c r="K60" s="38"/>
+      <c r="L60" s="15"/>
       <c r="M60" s="38"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="38"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="15"/>
       <c r="P60" s="38"/>
-      <c r="Q60" s="15"/>
-      <c r="R60" s="38"/>
+      <c r="Q60" s="38"/>
+      <c r="R60" s="15"/>
       <c r="S60" s="38"/>
-      <c r="T60" s="15"/>
-      <c r="U60" s="38"/>
+      <c r="T60" s="38"/>
+      <c r="U60" s="15"/>
       <c r="V60" s="38"/>
-      <c r="W60" s="15"/>
-      <c r="X60" s="38"/>
+      <c r="W60" s="38"/>
+      <c r="X60" s="15"/>
       <c r="Y60" s="38"/>
-      <c r="Z60" s="16">
+      <c r="Z60" s="38"/>
+      <c r="AA60" s="16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA60" s="16">
+      <c r="AB60" s="16">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Documents/HU, HT, PB, SB.xlsx
+++ b/Documents/HU, HT, PB, SB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ff47571d30268be/Documentos/6/APLICACIONE II/Proyecto/SIGDCOLTA/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{1529DF72-A3DE-466E-97C9-837D61FF45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A97973B-AEAA-4991-8C8B-B212378CB00D}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{1529DF72-A3DE-466E-97C9-837D61FF45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D581C6E8-6281-4DEC-BA8D-3294EBCD2F2B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="4" xr2:uid="{D7927580-9A21-4766-84F0-58BE9C7E4DF7}"/>
   </bookViews>
@@ -139,9 +139,6 @@
     <t>La identificación de entidades se realizó con precisión, sentando las bases para un diseño de base de datos coherente y efectivo.</t>
   </si>
   <si>
-    <t>La identificación de entidades principales y atributos se llevó a cabo de manera eficiente</t>
-  </si>
-  <si>
     <t>HU</t>
   </si>
   <si>
@@ -1736,6 +1733,9 @@
   </si>
   <si>
     <t>Sprint 3-4</t>
+  </si>
+  <si>
+    <t>La identificación posibles errores en las operaciones CRUD</t>
   </si>
 </sst>
 </file>
@@ -2338,6 +2338,94 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2347,57 +2435,6 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2416,27 +2453,6 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2455,22 +2471,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2811,55 +2811,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="92" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="94"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>53</v>
-      </c>
       <c r="F2" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="H2" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="I2" s="22" t="s">
         <v>57</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="37" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -2867,100 +2867,100 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="77" t="s">
+      <c r="A4" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="78" t="s">
+      <c r="D4" s="81" t="s">
         <v>69</v>
-      </c>
-      <c r="D4" s="79" t="s">
-        <v>70</v>
       </c>
       <c r="E4" s="26">
         <v>1</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="79"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="81"/>
       <c r="E5" s="26">
         <v>2</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G5" s="23"/>
       <c r="H5" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="79"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="81"/>
       <c r="E6" s="26">
         <v>3</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="77"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="79"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="81"/>
       <c r="E7" s="26">
         <v>4</v>
       </c>
       <c r="F7" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="H7" s="23" t="s">
         <v>541</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="I7" s="23" t="s">
         <v>542</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31"/>
-      <c r="B8" s="63" t="s">
-        <v>330</v>
-      </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
+      <c r="B8" s="93" t="s">
+        <v>329</v>
+      </c>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -2968,141 +2968,141 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="92" t="s">
         <v>76</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>77</v>
       </c>
       <c r="E9" s="26">
         <v>1</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
       <c r="E10" s="26">
         <v>2</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
       <c r="E11" s="26">
         <v>3</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
       <c r="E12" s="43"/>
       <c r="F12" s="23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
       <c r="E13" s="43"/>
       <c r="F13" s="61" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
       <c r="E14" s="43"/>
       <c r="F14" s="44" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G14" s="44"/>
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
     </row>
     <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="73"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
       <c r="E15" s="26">
         <v>4</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
-      <c r="B16" s="66" t="s">
-        <v>332</v>
-      </c>
-      <c r="C16" s="67"/>
-      <c r="D16" s="68"/>
+      <c r="B16" s="86" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="87"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="27"/>
       <c r="F16" s="62"/>
       <c r="G16" s="28"/>
@@ -3110,116 +3110,116 @@
       <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="74" t="s">
+      <c r="A17" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="89" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="66" t="s">
         <v>80</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>81</v>
       </c>
       <c r="E17" s="26">
         <v>1</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="72"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="70"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="66"/>
       <c r="E18" s="26">
         <v>2</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G18" s="23"/>
       <c r="H18" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="72"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="70"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="66"/>
       <c r="E19" s="43"/>
       <c r="F19" s="44" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
-      <c r="B20" s="70"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="70"/>
+      <c r="A20" s="71"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="66"/>
       <c r="E20" s="26">
         <v>3</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="70"/>
+      <c r="A21" s="71"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="66"/>
       <c r="E21" s="26">
         <v>4</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="73"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="70"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="66"/>
       <c r="E22" s="43"/>
       <c r="F22" s="44" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G22" s="44"/>
       <c r="H22" s="44"/>
@@ -3227,11 +3227,11 @@
     </row>
     <row r="23" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
-      <c r="B23" s="63" t="s">
-        <v>328</v>
-      </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="65"/>
+      <c r="B23" s="93" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" s="94"/>
+      <c r="D23" s="95"/>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
@@ -3239,98 +3239,98 @@
       <c r="I23" s="28"/>
     </row>
     <row r="24" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="77" t="s">
+      <c r="A24" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="78" t="s">
+      <c r="D24" s="81" t="s">
         <v>72</v>
-      </c>
-      <c r="D24" s="79" t="s">
-        <v>73</v>
       </c>
       <c r="E24" s="26">
         <v>1</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="77"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
+      <c r="A25" s="79"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="34">
         <v>2</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="77"/>
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
+      <c r="A26" s="79"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="81"/>
       <c r="E26" s="26">
         <v>3</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
+      <c r="A27" s="79"/>
+      <c r="B27" s="79"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="81"/>
       <c r="E27" s="26">
         <v>4</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30"/>
-      <c r="B28" s="63" t="s">
-        <v>329</v>
-      </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="65"/>
+      <c r="B28" s="93" t="s">
+        <v>328</v>
+      </c>
+      <c r="C28" s="94"/>
+      <c r="D28" s="95"/>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
@@ -3338,214 +3338,214 @@
       <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="83" t="s">
+      <c r="A29" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="99" t="s">
         <v>74</v>
-      </c>
-      <c r="D29" s="86" t="s">
-        <v>75</v>
       </c>
       <c r="E29" s="26">
         <v>1</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="81"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="87"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="97"/>
+      <c r="D30" s="100"/>
       <c r="E30" s="26">
         <v>2</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="81"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="84"/>
-      <c r="D31" s="87"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="100"/>
       <c r="E31" s="26">
         <v>3</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="88"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="101"/>
       <c r="E32" s="26">
         <v>4</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
-      <c r="B33" s="66" t="s">
-        <v>331</v>
-      </c>
-      <c r="C33" s="67"/>
-      <c r="D33" s="68"/>
+      <c r="B33" s="86" t="s">
+        <v>330</v>
+      </c>
+      <c r="C33" s="87"/>
+      <c r="D33" s="88"/>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="28"/>
     </row>
-    <row r="34" spans="1:9" s="103" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="70" t="s">
+    <row r="34" spans="1:9" s="64" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="104" t="s">
-        <v>79</v>
-      </c>
       <c r="E34" s="34"/>
-      <c r="F34" s="102" t="s">
-        <v>559</v>
-      </c>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
+      <c r="F34" s="63" t="s">
+        <v>558</v>
+      </c>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="105"/>
+      <c r="A35" s="71"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="68"/>
       <c r="E35" s="26">
         <v>1</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="72"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="105"/>
+      <c r="A36" s="71"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="68"/>
       <c r="E36" s="26">
         <v>2</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="72"/>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="105"/>
+      <c r="A37" s="71"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="68"/>
       <c r="E37" s="26">
         <v>3</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="73"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="106"/>
+      <c r="A38" s="72"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="69"/>
       <c r="E38" s="26">
         <v>4</v>
       </c>
       <c r="F38" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="G38" s="23" t="s">
         <v>562</v>
       </c>
-      <c r="G38" s="23" t="s">
-        <v>563</v>
-      </c>
       <c r="H38" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
-      <c r="B39" s="66" t="s">
-        <v>333</v>
-      </c>
-      <c r="C39" s="67"/>
-      <c r="D39" s="68"/>
+      <c r="B39" s="86" t="s">
+        <v>332</v>
+      </c>
+      <c r="C39" s="87"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="27"/>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
@@ -3553,100 +3553,100 @@
       <c r="I39" s="28"/>
     </row>
     <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="70" t="s">
+      <c r="A40" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="69" t="s">
+      <c r="D40" s="92" t="s">
         <v>83</v>
-      </c>
-      <c r="D40" s="69" t="s">
-        <v>84</v>
       </c>
       <c r="E40" s="26">
         <v>1</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="72"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
+      <c r="A41" s="71"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
       <c r="E41" s="26">
         <v>2</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G41" s="24"/>
       <c r="H41" s="24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="72"/>
-      <c r="B42" s="70"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
+      <c r="A42" s="71"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="92"/>
       <c r="E42" s="26">
         <v>3</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="73"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
+      <c r="A43" s="72"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
       <c r="E43" s="26">
         <v>4</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
-      <c r="B44" s="66" t="s">
-        <v>334</v>
-      </c>
-      <c r="C44" s="67"/>
-      <c r="D44" s="68"/>
+      <c r="B44" s="86" t="s">
+        <v>333</v>
+      </c>
+      <c r="C44" s="87"/>
+      <c r="D44" s="88"/>
       <c r="E44" s="27"/>
       <c r="F44" s="33"/>
       <c r="G44" s="33"/>
@@ -3654,104 +3654,104 @@
       <c r="I44" s="33"/>
     </row>
     <row r="45" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="69" t="s">
+      <c r="A45" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="92" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="92" t="s">
         <v>85</v>
-      </c>
-      <c r="D45" s="69" t="s">
-        <v>86</v>
       </c>
       <c r="E45" s="26">
         <v>1</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72"/>
-      <c r="B46" s="70"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
+      <c r="A46" s="71"/>
+      <c r="B46" s="66"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="92"/>
       <c r="E46" s="26">
         <v>2</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="72"/>
-      <c r="B47" s="70"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
+      <c r="A47" s="71"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="92"/>
       <c r="E47" s="26">
         <v>3</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="73"/>
-      <c r="B48" s="70"/>
-      <c r="C48" s="69"/>
-      <c r="D48" s="69"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="92"/>
       <c r="E48" s="26">
         <v>4</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32"/>
-      <c r="B49" s="66" t="s">
-        <v>335</v>
-      </c>
-      <c r="C49" s="67"/>
-      <c r="D49" s="68"/>
+      <c r="B49" s="86" t="s">
+        <v>334</v>
+      </c>
+      <c r="C49" s="87"/>
+      <c r="D49" s="88"/>
       <c r="E49" s="27"/>
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
@@ -3759,102 +3759,102 @@
       <c r="I49" s="33"/>
     </row>
     <row r="50" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="70" t="s">
+      <c r="A50" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="92" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="D50" s="92" t="s">
         <v>88</v>
-      </c>
-      <c r="D50" s="69" t="s">
-        <v>89</v>
       </c>
       <c r="E50" s="26">
         <v>1</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="69"/>
-      <c r="D51" s="69"/>
+      <c r="A51" s="71"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
       <c r="E51" s="26">
         <v>2</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G51" s="24"/>
       <c r="H51" s="24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="72"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
+      <c r="A52" s="71"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="92"/>
       <c r="E52" s="26">
         <v>3</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="73"/>
-      <c r="B53" s="70"/>
-      <c r="C53" s="69"/>
-      <c r="D53" s="69"/>
+      <c r="A53" s="72"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="92"/>
       <c r="E53" s="26">
         <v>4</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="32"/>
-      <c r="B54" s="66" t="s">
-        <v>336</v>
-      </c>
-      <c r="C54" s="67"/>
-      <c r="D54" s="68"/>
+      <c r="B54" s="86" t="s">
+        <v>335</v>
+      </c>
+      <c r="C54" s="87"/>
+      <c r="D54" s="88"/>
       <c r="E54" s="27"/>
       <c r="F54" s="33"/>
       <c r="G54" s="33"/>
@@ -3862,104 +3862,104 @@
       <c r="I54" s="33"/>
     </row>
     <row r="55" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="70" t="s">
+      <c r="A55" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="D55" s="92" t="s">
         <v>91</v>
-      </c>
-      <c r="D55" s="69" t="s">
-        <v>92</v>
       </c>
       <c r="E55" s="26">
         <v>1</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="A56" s="71"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
       <c r="E56" s="26">
         <v>2</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="69"/>
+      <c r="A57" s="71"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="92"/>
+      <c r="D57" s="92"/>
       <c r="E57" s="26">
         <v>3</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="73"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="69"/>
+      <c r="A58" s="72"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="92"/>
+      <c r="D58" s="92"/>
       <c r="E58" s="26">
         <v>4</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="32"/>
-      <c r="B59" s="66" t="s">
-        <v>337</v>
-      </c>
-      <c r="C59" s="67"/>
-      <c r="D59" s="68"/>
+      <c r="B59" s="86" t="s">
+        <v>336</v>
+      </c>
+      <c r="C59" s="87"/>
+      <c r="D59" s="88"/>
       <c r="E59" s="27"/>
       <c r="F59" s="33"/>
       <c r="G59" s="33"/>
@@ -3967,102 +3967,102 @@
       <c r="I59" s="33"/>
     </row>
     <row r="60" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="71" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" s="69" t="s">
+      <c r="A60" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="92" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="92" t="s">
         <v>93</v>
-      </c>
-      <c r="D60" s="69" t="s">
-        <v>94</v>
       </c>
       <c r="E60" s="26">
         <v>1</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G60" s="24"/>
       <c r="H60" s="24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="70"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
+      <c r="A61" s="71"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="92"/>
+      <c r="D61" s="92"/>
       <c r="E61" s="26">
         <v>2</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="70"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="69"/>
+      <c r="A62" s="71"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
       <c r="E62" s="26">
         <v>3</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="73"/>
-      <c r="B63" s="70"/>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
+      <c r="A63" s="72"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="92"/>
+      <c r="D63" s="92"/>
       <c r="E63" s="26">
         <v>4</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="32"/>
-      <c r="B64" s="66" t="s">
-        <v>338</v>
-      </c>
-      <c r="C64" s="67"/>
-      <c r="D64" s="68"/>
+      <c r="B64" s="86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" s="87"/>
+      <c r="D64" s="88"/>
       <c r="E64" s="27"/>
       <c r="F64" s="33"/>
       <c r="G64" s="33"/>
@@ -4070,104 +4070,104 @@
       <c r="I64" s="33"/>
     </row>
     <row r="65" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B65" s="70" t="s">
+      <c r="A65" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="C65" s="69" t="s">
+      <c r="D65" s="92" t="s">
         <v>96</v>
-      </c>
-      <c r="D65" s="69" t="s">
-        <v>97</v>
       </c>
       <c r="E65" s="26">
         <v>1</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="70"/>
-      <c r="C66" s="69"/>
-      <c r="D66" s="69"/>
+      <c r="A66" s="71"/>
+      <c r="B66" s="66"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
       <c r="E66" s="26">
         <v>2</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="72"/>
-      <c r="B67" s="70"/>
-      <c r="C67" s="69"/>
-      <c r="D67" s="69"/>
+      <c r="A67" s="71"/>
+      <c r="B67" s="66"/>
+      <c r="C67" s="92"/>
+      <c r="D67" s="92"/>
       <c r="E67" s="26">
         <v>3</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="73"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="69"/>
+      <c r="A68" s="72"/>
+      <c r="B68" s="66"/>
+      <c r="C68" s="92"/>
+      <c r="D68" s="92"/>
       <c r="E68" s="26">
         <v>4</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32"/>
-      <c r="B69" s="66" t="s">
-        <v>339</v>
-      </c>
-      <c r="C69" s="67"/>
-      <c r="D69" s="68"/>
+      <c r="B69" s="86" t="s">
+        <v>338</v>
+      </c>
+      <c r="C69" s="87"/>
+      <c r="D69" s="88"/>
       <c r="E69" s="27"/>
       <c r="F69" s="33"/>
       <c r="G69" s="33"/>
@@ -4175,100 +4175,100 @@
       <c r="I69" s="33"/>
     </row>
     <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="71" t="s">
+      <c r="A70" s="70" t="s">
+        <v>97</v>
+      </c>
+      <c r="B70" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="70" t="s">
+      <c r="C70" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="69" t="s">
+      <c r="D70" s="92" t="s">
         <v>100</v>
-      </c>
-      <c r="D70" s="69" t="s">
-        <v>101</v>
       </c>
       <c r="E70" s="26">
         <v>1</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="70"/>
-      <c r="C71" s="69"/>
-      <c r="D71" s="69"/>
+      <c r="A71" s="71"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="92"/>
+      <c r="D71" s="92"/>
       <c r="E71" s="26">
         <v>2</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G71" s="24"/>
       <c r="H71" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="70"/>
-      <c r="C72" s="69"/>
-      <c r="D72" s="69"/>
+      <c r="A72" s="71"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="92"/>
+      <c r="D72" s="92"/>
       <c r="E72" s="26">
         <v>3</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G72" s="24"/>
       <c r="H72" s="24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="73"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="69"/>
-      <c r="D73" s="69"/>
+      <c r="A73" s="72"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="92"/>
       <c r="E73" s="26">
         <v>4</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32"/>
-      <c r="B74" s="66" t="s">
-        <v>340</v>
-      </c>
-      <c r="C74" s="67"/>
-      <c r="D74" s="68"/>
+      <c r="B74" s="86" t="s">
+        <v>339</v>
+      </c>
+      <c r="C74" s="87"/>
+      <c r="D74" s="88"/>
       <c r="E74" s="27"/>
       <c r="F74" s="33"/>
       <c r="G74" s="33"/>
@@ -4276,104 +4276,104 @@
       <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="71" t="s">
+      <c r="A75" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="B75" s="70" t="s">
+      <c r="C75" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="69" t="s">
+      <c r="D75" s="92" t="s">
         <v>104</v>
-      </c>
-      <c r="D75" s="69" t="s">
-        <v>105</v>
       </c>
       <c r="E75" s="26">
         <v>1</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I75" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="70"/>
-      <c r="C76" s="69"/>
-      <c r="D76" s="69"/>
+      <c r="A76" s="71"/>
+      <c r="B76" s="66"/>
+      <c r="C76" s="92"/>
+      <c r="D76" s="92"/>
       <c r="E76" s="26">
         <v>2</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I76" s="24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="70"/>
-      <c r="C77" s="69"/>
-      <c r="D77" s="69"/>
+      <c r="A77" s="71"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="92"/>
+      <c r="D77" s="92"/>
       <c r="E77" s="26">
         <v>3</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="73"/>
-      <c r="B78" s="70"/>
-      <c r="C78" s="69"/>
-      <c r="D78" s="69"/>
+      <c r="A78" s="72"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="92"/>
+      <c r="D78" s="92"/>
       <c r="E78" s="26">
         <v>4</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I78" s="24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="32"/>
-      <c r="B79" s="66" t="s">
-        <v>341</v>
-      </c>
-      <c r="C79" s="67"/>
-      <c r="D79" s="68"/>
+      <c r="B79" s="86" t="s">
+        <v>340</v>
+      </c>
+      <c r="C79" s="87"/>
+      <c r="D79" s="88"/>
       <c r="E79" s="27"/>
       <c r="F79" s="33"/>
       <c r="G79" s="33"/>
@@ -4381,104 +4381,104 @@
       <c r="I79" s="33"/>
     </row>
     <row r="80" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C80" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C80" s="69" t="s">
+      <c r="D80" s="92" t="s">
         <v>107</v>
-      </c>
-      <c r="D80" s="69" t="s">
-        <v>108</v>
       </c>
       <c r="E80" s="26">
         <v>1</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I80" s="24" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="72"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="69"/>
+      <c r="A81" s="71"/>
+      <c r="B81" s="66"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
       <c r="E81" s="26">
         <v>2</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I81" s="24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="72"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="69"/>
+      <c r="A82" s="71"/>
+      <c r="B82" s="66"/>
+      <c r="C82" s="92"/>
+      <c r="D82" s="92"/>
       <c r="E82" s="26">
         <v>3</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I82" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="73"/>
-      <c r="B83" s="70"/>
-      <c r="C83" s="69"/>
-      <c r="D83" s="69"/>
+      <c r="A83" s="72"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="92"/>
+      <c r="D83" s="92"/>
       <c r="E83" s="26">
         <v>4</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I83" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="32"/>
-      <c r="B84" s="66" t="s">
-        <v>342</v>
-      </c>
-      <c r="C84" s="67"/>
-      <c r="D84" s="68"/>
+      <c r="B84" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="C84" s="87"/>
+      <c r="D84" s="88"/>
       <c r="E84" s="27"/>
       <c r="F84" s="33"/>
       <c r="G84" s="33"/>
@@ -4486,115 +4486,144 @@
       <c r="I84" s="33"/>
     </row>
     <row r="85" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="71" t="s">
+      <c r="A85" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="B85" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="B85" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="C85" s="69" t="s">
+      <c r="D85" s="92" t="s">
         <v>110</v>
-      </c>
-      <c r="D85" s="69" t="s">
-        <v>111</v>
       </c>
       <c r="E85" s="26">
         <v>1</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I85" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="70"/>
-      <c r="C86" s="69"/>
-      <c r="D86" s="69"/>
+      <c r="A86" s="71"/>
+      <c r="B86" s="66"/>
+      <c r="C86" s="92"/>
+      <c r="D86" s="92"/>
       <c r="E86" s="26">
         <v>2</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="70"/>
-      <c r="C87" s="69"/>
-      <c r="D87" s="69"/>
+      <c r="A87" s="71"/>
+      <c r="B87" s="66"/>
+      <c r="C87" s="92"/>
+      <c r="D87" s="92"/>
       <c r="E87" s="26">
         <v>3</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I87" s="24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="73"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="69"/>
-      <c r="D88" s="69"/>
+      <c r="A88" s="72"/>
+      <c r="B88" s="66"/>
+      <c r="C88" s="92"/>
+      <c r="D88" s="92"/>
       <c r="E88" s="26">
         <v>4</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="D65:D68"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="C60:C63"/>
     <mergeCell ref="B45:B48"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="B16:D16"/>
@@ -4611,51 +4640,22 @@
     <mergeCell ref="C29:C32"/>
     <mergeCell ref="D29:D32"/>
     <mergeCell ref="B34:B38"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="A85:A88"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="D85:D88"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="D75:D78"/>
-    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A9:A15"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="D9:D15"/>
@@ -4685,55 +4685,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="92" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="94"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="D2" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="E2" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="42" t="s">
-        <v>53</v>
-      </c>
       <c r="F2" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="H2" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="I2" s="22" t="s">
         <v>57</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -4741,60 +4741,60 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="83" t="s">
+      <c r="A4" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="96" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" s="96" t="s">
         <v>462</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="D4" s="96" t="s">
         <v>463</v>
-      </c>
-      <c r="D4" s="83" t="s">
-        <v>464</v>
       </c>
       <c r="E4" s="40">
         <v>1</v>
       </c>
       <c r="F4" s="41" t="s">
+        <v>475</v>
+      </c>
+      <c r="G4" s="41" t="s">
         <v>476</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="H4" s="41" t="s">
         <v>477</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="I4" s="41" t="s">
         <v>478</v>
       </c>
-      <c r="I4" s="41" t="s">
-        <v>479</v>
-      </c>
     </row>
     <row r="5" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
       <c r="E5" s="40">
         <v>2</v>
       </c>
       <c r="F5" s="41" t="s">
+        <v>479</v>
+      </c>
+      <c r="G5" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="H5" s="41" t="s">
         <v>481</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="I5" s="41" t="s">
         <v>482</v>
       </c>
-      <c r="I5" s="41" t="s">
-        <v>483</v>
-      </c>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="77"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
       <c r="E6" s="40">
         <v>3</v>
       </c>
@@ -4804,10 +4804,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="77"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
       <c r="E7" s="40">
         <v>4</v>
       </c>
@@ -4818,11 +4818,11 @@
     </row>
     <row r="8" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
-      <c r="B8" s="97" t="s">
-        <v>328</v>
-      </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="99"/>
+      <c r="B8" s="103" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="104"/>
+      <c r="D8" s="105"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -4830,60 +4830,60 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="83" t="s">
+      <c r="A9" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="96" t="s">
+        <v>464</v>
+      </c>
+      <c r="C9" s="96" t="s">
         <v>465</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="D9" s="96" t="s">
         <v>466</v>
-      </c>
-      <c r="D9" s="83" t="s">
-        <v>467</v>
       </c>
       <c r="E9" s="40">
         <v>1</v>
       </c>
       <c r="F9" s="41" t="s">
+        <v>483</v>
+      </c>
+      <c r="G9" s="41" t="s">
         <v>484</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="H9" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="I9" s="41" t="s">
         <v>486</v>
       </c>
-      <c r="I9" s="41" t="s">
-        <v>487</v>
-      </c>
     </row>
     <row r="10" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="77"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
+      <c r="A10" s="79"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
       <c r="E10" s="34">
         <v>2</v>
       </c>
       <c r="F10" s="41" t="s">
+        <v>487</v>
+      </c>
+      <c r="G10" s="41" t="s">
         <v>488</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="H10" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="I10" s="41" t="s">
         <v>490</v>
       </c>
-      <c r="I10" s="41" t="s">
-        <v>491</v>
-      </c>
     </row>
     <row r="11" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
+      <c r="A11" s="79"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
       <c r="E11" s="40">
         <v>3</v>
       </c>
@@ -4893,10 +4893,10 @@
       <c r="I11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
+      <c r="A12" s="79"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
       <c r="E12" s="40">
         <v>4</v>
       </c>
@@ -4907,11 +4907,11 @@
     </row>
     <row r="13" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35"/>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
       <c r="E13" s="35"/>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
@@ -4919,81 +4919,81 @@
       <c r="I13" s="36"/>
     </row>
     <row r="14" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="83" t="s">
+      <c r="A14" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="96" t="s">
+        <v>467</v>
+      </c>
+      <c r="C14" s="96" t="s">
         <v>468</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="D14" s="96" t="s">
         <v>469</v>
-      </c>
-      <c r="D14" s="83" t="s">
-        <v>470</v>
       </c>
       <c r="E14" s="40">
         <v>1</v>
       </c>
       <c r="F14" s="41" t="s">
+        <v>491</v>
+      </c>
+      <c r="G14" s="41" t="s">
         <v>492</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="H14" s="41" t="s">
         <v>493</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="I14" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="I14" s="41" t="s">
-        <v>495</v>
-      </c>
     </row>
     <row r="15" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
+      <c r="A15" s="79"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="97"/>
       <c r="E15" s="40">
         <v>2</v>
       </c>
       <c r="F15" s="41" t="s">
+        <v>495</v>
+      </c>
+      <c r="G15" s="41" t="s">
         <v>496</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="H15" s="41" t="s">
         <v>497</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="I15" s="41" t="s">
         <v>498</v>
       </c>
-      <c r="I15" s="41" t="s">
-        <v>499</v>
-      </c>
     </row>
     <row r="16" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="77"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
+      <c r="A16" s="79"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
       <c r="E16" s="40">
         <v>3</v>
       </c>
       <c r="F16" s="41" t="s">
+        <v>499</v>
+      </c>
+      <c r="G16" s="41" t="s">
         <v>500</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="H16" s="41" t="s">
         <v>501</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="I16" s="41" t="s">
         <v>502</v>
       </c>
-      <c r="I16" s="41" t="s">
-        <v>503</v>
-      </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="77"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
+      <c r="A17" s="79"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
       <c r="E17" s="40">
         <v>4</v>
       </c>
@@ -5004,11 +5004,11 @@
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
-      <c r="B18" s="96" t="s">
+      <c r="B18" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
       <c r="E18" s="35"/>
       <c r="F18" s="36"/>
       <c r="G18" s="36"/>
@@ -5016,81 +5016,81 @@
       <c r="I18" s="36"/>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="83" t="s">
-        <v>468</v>
-      </c>
-      <c r="C19" s="83" t="s">
+      <c r="A19" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="96" t="s">
+        <v>467</v>
+      </c>
+      <c r="C19" s="96" t="s">
+        <v>470</v>
+      </c>
+      <c r="D19" s="96" t="s">
         <v>471</v>
-      </c>
-      <c r="D19" s="83" t="s">
-        <v>472</v>
       </c>
       <c r="E19" s="40">
         <v>1</v>
       </c>
       <c r="F19" s="41" t="s">
+        <v>503</v>
+      </c>
+      <c r="G19" s="41" t="s">
         <v>504</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="H19" s="41" t="s">
         <v>505</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="I19" s="41" t="s">
         <v>506</v>
       </c>
-      <c r="I19" s="41" t="s">
-        <v>507</v>
-      </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="77"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
+      <c r="A20" s="79"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
       <c r="E20" s="40">
         <v>2</v>
       </c>
       <c r="F20" s="41" t="s">
+        <v>507</v>
+      </c>
+      <c r="G20" s="41" t="s">
         <v>508</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="H20" s="41" t="s">
         <v>509</v>
       </c>
-      <c r="H20" s="41" t="s">
+      <c r="I20" s="41" t="s">
         <v>510</v>
       </c>
-      <c r="I20" s="41" t="s">
-        <v>511</v>
-      </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="77"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="84"/>
+      <c r="A21" s="79"/>
+      <c r="B21" s="97"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="97"/>
       <c r="E21" s="40">
         <v>3</v>
       </c>
       <c r="F21" s="41" t="s">
+        <v>511</v>
+      </c>
+      <c r="G21" s="41" t="s">
         <v>512</v>
       </c>
-      <c r="G21" s="41" t="s">
+      <c r="H21" s="41" t="s">
         <v>513</v>
       </c>
-      <c r="H21" s="41" t="s">
+      <c r="I21" s="41" t="s">
         <v>514</v>
       </c>
-      <c r="I21" s="41" t="s">
-        <v>515</v>
-      </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
+      <c r="A22" s="79"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
       <c r="E22" s="40">
         <v>4</v>
       </c>
@@ -5101,11 +5101,11 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
-      <c r="B23" s="96" t="s">
+      <c r="B23" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
       <c r="E23" s="35"/>
       <c r="F23" s="36"/>
       <c r="G23" s="36"/>
@@ -5113,154 +5113,141 @@
       <c r="I23" s="36"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="80" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="80" t="s">
+      <c r="A24" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="83" t="s">
+        <v>472</v>
+      </c>
+      <c r="C24" s="83" t="s">
         <v>473</v>
       </c>
-      <c r="C24" s="80" t="s">
+      <c r="D24" s="83" t="s">
         <v>474</v>
-      </c>
-      <c r="D24" s="80" t="s">
-        <v>475</v>
       </c>
       <c r="E24" s="40">
         <v>1</v>
       </c>
       <c r="F24" s="41" t="s">
+        <v>515</v>
+      </c>
+      <c r="G24" s="41" t="s">
         <v>516</v>
       </c>
-      <c r="G24" s="41" t="s">
+      <c r="H24" s="41" t="s">
         <v>517</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="I24" s="41" t="s">
         <v>518</v>
       </c>
-      <c r="I24" s="41" t="s">
-        <v>519</v>
-      </c>
     </row>
     <row r="25" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="81"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="81"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
       <c r="E25" s="40">
         <v>2</v>
       </c>
       <c r="F25" s="41" t="s">
+        <v>519</v>
+      </c>
+      <c r="G25" s="41" t="s">
         <v>520</v>
       </c>
-      <c r="G25" s="41" t="s">
+      <c r="H25" s="41" t="s">
         <v>521</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="I25" s="41" t="s">
         <v>522</v>
       </c>
-      <c r="I25" s="41" t="s">
-        <v>523</v>
-      </c>
     </row>
     <row r="26" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="81"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
       <c r="E26" s="40">
         <v>3</v>
       </c>
       <c r="F26" s="41" t="s">
+        <v>523</v>
+      </c>
+      <c r="G26" s="41" t="s">
         <v>524</v>
       </c>
-      <c r="G26" s="41" t="s">
+      <c r="H26" s="41" t="s">
         <v>525</v>
       </c>
-      <c r="H26" s="41" t="s">
+      <c r="I26" s="41" t="s">
         <v>526</v>
       </c>
-      <c r="I26" s="41" t="s">
-        <v>527</v>
-      </c>
     </row>
     <row r="27" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="81"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
       <c r="E27" s="40">
         <v>4</v>
       </c>
       <c r="F27" s="41" t="s">
+        <v>527</v>
+      </c>
+      <c r="G27" s="41" t="s">
         <v>528</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="H27" s="41" t="s">
         <v>529</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="I27" s="41" t="s">
         <v>530</v>
       </c>
-      <c r="I27" s="41" t="s">
-        <v>531</v>
-      </c>
     </row>
     <row r="28" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="81"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
       <c r="E28" s="40">
         <v>5</v>
       </c>
       <c r="F28" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>535</v>
-      </c>
     </row>
     <row r="29" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="82"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
       <c r="E29" s="40">
         <v>6</v>
       </c>
       <c r="F29" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>539</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
     <mergeCell ref="D24:D29"/>
     <mergeCell ref="C24:C29"/>
     <mergeCell ref="B24:B29"/>
@@ -5275,6 +5262,19 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5306,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -5324,24 +5324,24 @@
         <v>6</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" s="53" t="s">
         <v>26</v>
@@ -5356,27 +5356,27 @@
         <v>31</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>355</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="53" t="s">
         <v>357</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>358</v>
       </c>
       <c r="F3" s="54" t="s">
         <v>27</v>
@@ -5385,27 +5385,27 @@
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J3" s="39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="53" t="s">
         <v>26</v>
@@ -5420,342 +5420,342 @@
         <v>32</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J4" s="39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C5" s="54" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="53" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G5" s="53" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>33</v>
+        <v>565</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J5" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="39" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J6" s="39" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="39" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="39" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J9" s="52" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="J10" s="52" t="s">
         <v>382</v>
-      </c>
-      <c r="J10" s="52" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F12" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G13" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F14" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B15" s="47" t="s">
+        <v>404</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>405</v>
       </c>
-      <c r="C15" s="52" t="s">
-        <v>342</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>406</v>
-      </c>
       <c r="E15" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F15" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G15" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -5790,112 +5790,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="100" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="101"/>
-      <c r="J1" s="100" t="s">
+      <c r="G1" s="106" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="107"/>
+      <c r="J1" s="106" t="s">
+        <v>345</v>
+      </c>
+      <c r="K1" s="107"/>
+      <c r="M1" s="106" t="s">
         <v>346</v>
       </c>
-      <c r="K1" s="101"/>
-      <c r="M1" s="100" t="s">
+      <c r="N1" s="107"/>
+      <c r="P1" s="106" t="s">
         <v>347</v>
       </c>
-      <c r="N1" s="101"/>
-      <c r="P1" s="100" t="s">
+      <c r="Q1" s="107"/>
+      <c r="S1" s="106" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="101"/>
-      <c r="S1" s="100" t="s">
+      <c r="T1" s="107"/>
+      <c r="V1" s="106" t="s">
         <v>349</v>
       </c>
-      <c r="T1" s="101"/>
-      <c r="V1" s="100" t="s">
+      <c r="W1" s="107"/>
+      <c r="Y1" s="106" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="101"/>
-      <c r="Y1" s="100" t="s">
-        <v>351</v>
-      </c>
-      <c r="Z1" s="101"/>
+      <c r="Z1" s="107"/>
     </row>
     <row r="2" spans="1:31" s="17" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U2" s="12"/>
       <c r="V2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X2" s="12"/>
       <c r="Y2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -5974,7 +5974,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
@@ -6108,7 +6108,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -6164,23 +6164,23 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AE6" s="107"/>
+      <c r="AE6" s="65"/>
     </row>
     <row r="7" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D7" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="14"/>
@@ -6210,13 +6210,13 @@
       <c r="A8" s="2"/>
       <c r="B8" s="57"/>
       <c r="C8" s="50" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D8" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="14"/>
@@ -6246,13 +6246,13 @@
       <c r="A9" s="2"/>
       <c r="B9" s="57"/>
       <c r="C9" s="50" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D9" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="14"/>
@@ -6282,13 +6282,13 @@
       <c r="A10" s="2"/>
       <c r="B10" s="57"/>
       <c r="C10" s="50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D10" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="14"/>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="11" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B11" s="56" t="s">
         <v>8</v>
@@ -6328,7 +6328,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="14"/>
@@ -6391,7 +6391,7 @@
         <v>28</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="14"/>
@@ -6454,7 +6454,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="14"/>
@@ -6517,7 +6517,7 @@
         <v>28</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="14"/>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="15" spans="1:31" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B15" s="56" t="s">
         <v>9</v>
@@ -6584,7 +6584,7 @@
         <v>29</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="14"/>
@@ -6647,7 +6647,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="14"/>
@@ -6710,7 +6710,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="14"/>
@@ -6773,7 +6773,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="14"/>
@@ -6833,10 +6833,10 @@
         <v>22</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="38"/>
@@ -6878,10 +6878,10 @@
         <v>23</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="38"/>
@@ -6923,10 +6923,10 @@
         <v>24</v>
       </c>
       <c r="D21" s="54" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="38"/>
@@ -6968,10 +6968,10 @@
         <v>25</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="38"/>
@@ -7008,19 +7008,19 @@
     </row>
     <row r="23" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="38"/>
@@ -7059,13 +7059,13 @@
       <c r="A24" s="2"/>
       <c r="B24" s="58"/>
       <c r="C24" s="52" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="38"/>
@@ -7098,13 +7098,13 @@
       <c r="A25" s="2"/>
       <c r="B25" s="58"/>
       <c r="C25" s="52" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="38"/>
@@ -7137,13 +7137,13 @@
       <c r="A26" s="2"/>
       <c r="B26" s="58"/>
       <c r="C26" s="52" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="38"/>
@@ -7176,13 +7176,13 @@
       <c r="A27" s="2"/>
       <c r="B27" s="58"/>
       <c r="C27" s="52" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D27" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="38"/>
@@ -7215,13 +7215,13 @@
       <c r="A28" s="2"/>
       <c r="B28" s="58"/>
       <c r="C28" s="52" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D28" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="38"/>
@@ -7254,13 +7254,13 @@
       <c r="A29" s="4"/>
       <c r="B29" s="58"/>
       <c r="C29" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D29" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="38"/>
@@ -7299,13 +7299,13 @@
       <c r="A30" s="4"/>
       <c r="B30" s="58"/>
       <c r="C30" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D30" s="54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="38"/>
@@ -7342,19 +7342,19 @@
     </row>
     <row r="31" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B31" s="58" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D31" s="54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="38"/>
@@ -7393,13 +7393,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="58"/>
       <c r="C32" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="38"/>
@@ -7438,13 +7438,13 @@
       <c r="A33" s="2"/>
       <c r="B33" s="58"/>
       <c r="C33" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D33" s="54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E33" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="38"/>
@@ -7481,19 +7481,19 @@
     </row>
     <row r="34" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="38"/>
@@ -7531,13 +7531,13 @@
     <row r="35" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="58"/>
       <c r="C35" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="38"/>
@@ -7575,13 +7575,13 @@
     <row r="36" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="58"/>
       <c r="C36" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="38"/>
@@ -7618,19 +7618,19 @@
     </row>
     <row r="37" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B37" s="58" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="38"/>
@@ -7669,13 +7669,13 @@
       <c r="A38" s="2"/>
       <c r="B38" s="58"/>
       <c r="C38" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="38"/>
@@ -7714,13 +7714,13 @@
       <c r="A39" s="2"/>
       <c r="B39" s="58"/>
       <c r="C39" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="38"/>
@@ -7759,13 +7759,13 @@
       <c r="A40" s="2"/>
       <c r="B40" s="58"/>
       <c r="C40" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="38"/>
@@ -7802,19 +7802,19 @@
     </row>
     <row r="41" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B41" s="58" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="38"/>
@@ -7852,13 +7852,13 @@
     <row r="42" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="58"/>
       <c r="C42" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="38"/>
@@ -7896,13 +7896,13 @@
     <row r="43" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="58"/>
       <c r="C43" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D43" s="54" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E43" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="38"/>
@@ -7939,19 +7939,19 @@
     </row>
     <row r="44" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="38"/>
@@ -7990,13 +7990,13 @@
       <c r="A45" s="2"/>
       <c r="B45" s="58"/>
       <c r="C45" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D45" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="38"/>
@@ -8035,13 +8035,13 @@
       <c r="A46" s="2"/>
       <c r="B46" s="58"/>
       <c r="C46" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D46" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="38"/>
@@ -8078,19 +8078,19 @@
     </row>
     <row r="47" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B47" s="58" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="38"/>
@@ -8129,13 +8129,13 @@
       <c r="A48" s="48"/>
       <c r="B48" s="58"/>
       <c r="C48" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D48" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="38"/>
@@ -8167,13 +8167,13 @@
     <row r="49" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="58"/>
       <c r="C49" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E49" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="38"/>
@@ -8211,13 +8211,13 @@
     <row r="50" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="58"/>
       <c r="C50" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D50" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="38"/>
@@ -8249,13 +8249,13 @@
     <row r="51" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="58"/>
       <c r="C51" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D51" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E51" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="38"/>
@@ -8292,19 +8292,19 @@
     </row>
     <row r="52" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E52" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="38"/>
@@ -8343,13 +8343,13 @@
       <c r="A53" s="2"/>
       <c r="B53" s="58"/>
       <c r="C53" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D53" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E53" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="38"/>
@@ -8388,13 +8388,13 @@
       <c r="A54" s="2"/>
       <c r="B54" s="58"/>
       <c r="C54" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D54" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="38"/>
@@ -8431,19 +8431,19 @@
     </row>
     <row r="55" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="38"/>
@@ -8481,13 +8481,13 @@
     <row r="56" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="58"/>
       <c r="C56" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D56" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="38"/>
@@ -8526,13 +8526,13 @@
       <c r="A57" s="2"/>
       <c r="B57" s="58"/>
       <c r="C57" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E57" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="38"/>
@@ -8569,19 +8569,19 @@
     </row>
     <row r="58" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D58" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="38"/>
@@ -8620,13 +8620,13 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D59" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E59" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="38"/>
@@ -8665,13 +8665,13 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D60" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E60" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="38"/>

--- a/Documents/HU, HT, PB, SB.xlsx
+++ b/Documents/HU, HT, PB, SB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ff47571d30268be/Documentos/6/APLICACIONE II/Proyecto/SIGDCOLTA/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{1529DF72-A3DE-466E-97C9-837D61FF45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D581C6E8-6281-4DEC-BA8D-3294EBCD2F2B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8397588-E4C4-45ED-874D-5417E68B970B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="4" xr2:uid="{D7927580-9A21-4766-84F0-58BE9C7E4DF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="3" xr2:uid="{D7927580-9A21-4766-84F0-58BE9C7E4DF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="566">
   <si>
     <t>Identificador (ID) de la Historia</t>
   </si>
@@ -139,6 +139,9 @@
     <t>La identificación de entidades se realizó con precisión, sentando las bases para un diseño de base de datos coherente y efectivo.</t>
   </si>
   <si>
+    <t>La identificación de entidades principales y atributos se llevó a cabo de manera eficiente</t>
+  </si>
+  <si>
     <t>HU</t>
   </si>
   <si>
@@ -1732,10 +1735,7 @@
     <t>Implementar opción de registro mediante gmail</t>
   </si>
   <si>
-    <t>Sprint 3-4</t>
-  </si>
-  <si>
-    <t>La identificación posibles errores en las operaciones CRUD</t>
+    <t>2 dias</t>
   </si>
 </sst>
 </file>
@@ -2158,7 +2158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2348,6 +2348,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2357,15 +2435,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2384,74 +2453,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2811,55 +2814,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="78"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="101"/>
     </row>
     <row r="2" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="37" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -2867,100 +2870,100 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="79" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="80" t="s">
+      <c r="A4" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="C4" s="82" t="s">
         <v>69</v>
+      </c>
+      <c r="D4" s="83" t="s">
+        <v>70</v>
       </c>
       <c r="E4" s="26">
         <v>1</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="81"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="83"/>
       <c r="E5" s="26">
         <v>2</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G5" s="23"/>
       <c r="H5" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="81"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="83"/>
       <c r="E6" s="26">
         <v>3</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="79"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="81"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="83"/>
       <c r="E7" s="26">
         <v>4</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31"/>
-      <c r="B8" s="93" t="s">
-        <v>329</v>
-      </c>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
+      <c r="B8" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="79"/>
+      <c r="D8" s="80"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -2968,141 +2971,141 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="92" t="s">
+      <c r="A9" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="74" t="s">
         <v>76</v>
+      </c>
+      <c r="D9" s="74" t="s">
+        <v>77</v>
       </c>
       <c r="E9" s="26">
         <v>1</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="71"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
       <c r="E10" s="26">
         <v>2</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
       <c r="E11" s="26">
         <v>3</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="92"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
       <c r="E12" s="43"/>
       <c r="F12" s="23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="92"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
       <c r="E13" s="43"/>
       <c r="F13" s="61" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="92"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
       <c r="E14" s="43"/>
       <c r="F14" s="44" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G14" s="44"/>
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
     </row>
     <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
       <c r="E15" s="26">
         <v>4</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
-      <c r="B16" s="86" t="s">
-        <v>331</v>
-      </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="88"/>
+      <c r="B16" s="71" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
       <c r="E16" s="27"/>
       <c r="F16" s="62"/>
       <c r="G16" s="28"/>
@@ -3110,116 +3113,116 @@
       <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="89" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="66" t="s">
+      <c r="A17" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="75" t="s">
         <v>80</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>81</v>
       </c>
       <c r="E17" s="26">
         <v>1</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="71"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="66"/>
+      <c r="A18" s="68"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="70"/>
       <c r="E18" s="26">
         <v>2</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G18" s="23"/>
       <c r="H18" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="71"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="66"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="70"/>
       <c r="E19" s="43"/>
       <c r="F19" s="44" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="71"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="66"/>
+      <c r="A20" s="68"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="70"/>
       <c r="E20" s="26">
         <v>3</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="71"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="66"/>
+      <c r="A21" s="68"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="70"/>
       <c r="E21" s="26">
         <v>4</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="66"/>
+      <c r="A22" s="69"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="43"/>
       <c r="F22" s="44" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G22" s="44"/>
       <c r="H22" s="44"/>
@@ -3227,11 +3230,11 @@
     </row>
     <row r="23" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
-      <c r="B23" s="93" t="s">
-        <v>327</v>
-      </c>
-      <c r="C23" s="94"/>
-      <c r="D23" s="95"/>
+      <c r="B23" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
@@ -3239,98 +3242,98 @@
       <c r="I23" s="28"/>
     </row>
     <row r="24" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="80" t="s">
+      <c r="A24" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="81" t="s">
+      <c r="C24" s="82" t="s">
         <v>72</v>
+      </c>
+      <c r="D24" s="83" t="s">
+        <v>73</v>
       </c>
       <c r="E24" s="26">
         <v>1</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="79"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="81"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="83"/>
       <c r="E25" s="34">
         <v>2</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="79"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="81"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="83"/>
       <c r="E26" s="26">
         <v>3</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="79"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="81"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="83"/>
       <c r="E27" s="26">
         <v>4</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30"/>
-      <c r="B28" s="93" t="s">
-        <v>328</v>
-      </c>
-      <c r="C28" s="94"/>
-      <c r="D28" s="95"/>
+      <c r="B28" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
@@ -3338,100 +3341,100 @@
       <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="99" t="s">
+      <c r="A29" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="87" t="s">
         <v>74</v>
+      </c>
+      <c r="D29" s="90" t="s">
+        <v>75</v>
       </c>
       <c r="E29" s="26">
         <v>1</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="97"/>
-      <c r="D30" s="100"/>
+      <c r="A30" s="85"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="91"/>
       <c r="E30" s="26">
         <v>2</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
-      <c r="B31" s="84"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="100"/>
+      <c r="A31" s="85"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="91"/>
       <c r="E31" s="26">
         <v>3</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="101"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="92"/>
       <c r="E32" s="26">
         <v>4</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
-      <c r="B33" s="86" t="s">
-        <v>330</v>
-      </c>
-      <c r="C33" s="87"/>
-      <c r="D33" s="88"/>
+      <c r="B33" s="71" t="s">
+        <v>331</v>
+      </c>
+      <c r="C33" s="72"/>
+      <c r="D33" s="73"/>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
@@ -3439,113 +3442,113 @@
       <c r="I33" s="28"/>
     </row>
     <row r="34" spans="1:9" s="64" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="66" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="67" t="s">
+      <c r="A34" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="70" t="s">
         <v>78</v>
+      </c>
+      <c r="D34" s="93" t="s">
+        <v>79</v>
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="63" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G34" s="63"/>
       <c r="H34" s="63"/>
       <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="71"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="68"/>
+      <c r="A35" s="68"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="94"/>
       <c r="E35" s="26">
         <v>1</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="71"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="68"/>
+      <c r="A36" s="68"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="94"/>
       <c r="E36" s="26">
         <v>2</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="71"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="68"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="94"/>
       <c r="E37" s="26">
         <v>3</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="72"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="69"/>
+      <c r="A38" s="69"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="95"/>
       <c r="E38" s="26">
         <v>4</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
-      <c r="B39" s="86" t="s">
-        <v>332</v>
-      </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="88"/>
+      <c r="B39" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="C39" s="72"/>
+      <c r="D39" s="73"/>
       <c r="E39" s="27"/>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
@@ -3553,100 +3556,100 @@
       <c r="I39" s="28"/>
     </row>
     <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="92" t="s">
+      <c r="A40" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="92" t="s">
+      <c r="C40" s="74" t="s">
         <v>83</v>
+      </c>
+      <c r="D40" s="74" t="s">
+        <v>84</v>
       </c>
       <c r="E40" s="26">
         <v>1</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="71"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
+      <c r="A41" s="68"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="74"/>
       <c r="E41" s="26">
         <v>2</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G41" s="24"/>
       <c r="H41" s="24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71"/>
-      <c r="B42" s="66"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
+      <c r="A42" s="68"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
       <c r="E42" s="26">
         <v>3</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="72"/>
-      <c r="B43" s="66"/>
-      <c r="C43" s="92"/>
-      <c r="D43" s="92"/>
+      <c r="A43" s="69"/>
+      <c r="B43" s="70"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="74"/>
       <c r="E43" s="26">
         <v>4</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
-      <c r="B44" s="86" t="s">
-        <v>333</v>
-      </c>
-      <c r="C44" s="87"/>
-      <c r="D44" s="88"/>
+      <c r="B44" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="C44" s="72"/>
+      <c r="D44" s="73"/>
       <c r="E44" s="27"/>
       <c r="F44" s="33"/>
       <c r="G44" s="33"/>
@@ -3654,104 +3657,104 @@
       <c r="I44" s="33"/>
     </row>
     <row r="45" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" s="92" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="92" t="s">
+      <c r="A45" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="74" t="s">
         <v>85</v>
+      </c>
+      <c r="D45" s="74" t="s">
+        <v>86</v>
       </c>
       <c r="E45" s="26">
         <v>1</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="71"/>
-      <c r="B46" s="66"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="92"/>
+      <c r="A46" s="68"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
       <c r="E46" s="26">
         <v>2</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="71"/>
-      <c r="B47" s="66"/>
-      <c r="C47" s="92"/>
-      <c r="D47" s="92"/>
+      <c r="A47" s="68"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="74"/>
       <c r="E47" s="26">
         <v>3</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="72"/>
-      <c r="B48" s="66"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="92"/>
+      <c r="A48" s="69"/>
+      <c r="B48" s="70"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="74"/>
       <c r="E48" s="26">
         <v>4</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32"/>
-      <c r="B49" s="86" t="s">
-        <v>334</v>
-      </c>
-      <c r="C49" s="87"/>
-      <c r="D49" s="88"/>
+      <c r="B49" s="71" t="s">
+        <v>335</v>
+      </c>
+      <c r="C49" s="72"/>
+      <c r="D49" s="73"/>
       <c r="E49" s="27"/>
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
@@ -3759,102 +3762,102 @@
       <c r="I49" s="33"/>
     </row>
     <row r="50" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="92" t="s">
+      <c r="A50" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="D50" s="92" t="s">
+      <c r="C50" s="74" t="s">
         <v>88</v>
+      </c>
+      <c r="D50" s="74" t="s">
+        <v>89</v>
       </c>
       <c r="E50" s="26">
         <v>1</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="71"/>
-      <c r="B51" s="66"/>
-      <c r="C51" s="92"/>
-      <c r="D51" s="92"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="74"/>
       <c r="E51" s="26">
         <v>2</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G51" s="24"/>
       <c r="H51" s="24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="71"/>
-      <c r="B52" s="66"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="92"/>
+      <c r="A52" s="68"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="74"/>
+      <c r="D52" s="74"/>
       <c r="E52" s="26">
         <v>3</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="92"/>
-      <c r="D53" s="92"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="70"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="74"/>
       <c r="E53" s="26">
         <v>4</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="32"/>
-      <c r="B54" s="86" t="s">
-        <v>335</v>
-      </c>
-      <c r="C54" s="87"/>
-      <c r="D54" s="88"/>
+      <c r="B54" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="C54" s="72"/>
+      <c r="D54" s="73"/>
       <c r="E54" s="27"/>
       <c r="F54" s="33"/>
       <c r="G54" s="33"/>
@@ -3862,104 +3865,104 @@
       <c r="I54" s="33"/>
     </row>
     <row r="55" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="92" t="s">
+      <c r="A55" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="92" t="s">
+      <c r="C55" s="74" t="s">
         <v>91</v>
+      </c>
+      <c r="D55" s="74" t="s">
+        <v>92</v>
       </c>
       <c r="E55" s="26">
         <v>1</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="71"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="92"/>
-      <c r="D56" s="92"/>
+      <c r="A56" s="68"/>
+      <c r="B56" s="70"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="26">
         <v>2</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="92"/>
-      <c r="D57" s="92"/>
+      <c r="A57" s="68"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="74"/>
       <c r="E57" s="26">
         <v>3</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="66"/>
-      <c r="C58" s="92"/>
-      <c r="D58" s="92"/>
+      <c r="A58" s="69"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="74"/>
+      <c r="D58" s="74"/>
       <c r="E58" s="26">
         <v>4</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="32"/>
-      <c r="B59" s="86" t="s">
-        <v>336</v>
-      </c>
-      <c r="C59" s="87"/>
-      <c r="D59" s="88"/>
+      <c r="B59" s="71" t="s">
+        <v>337</v>
+      </c>
+      <c r="C59" s="72"/>
+      <c r="D59" s="73"/>
       <c r="E59" s="27"/>
       <c r="F59" s="33"/>
       <c r="G59" s="33"/>
@@ -3967,102 +3970,102 @@
       <c r="I59" s="33"/>
     </row>
     <row r="60" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="92" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="92" t="s">
+      <c r="A60" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="74" t="s">
         <v>93</v>
+      </c>
+      <c r="D60" s="74" t="s">
+        <v>94</v>
       </c>
       <c r="E60" s="26">
         <v>1</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G60" s="24"/>
       <c r="H60" s="24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="71"/>
-      <c r="B61" s="66"/>
-      <c r="C61" s="92"/>
-      <c r="D61" s="92"/>
+      <c r="A61" s="68"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="74"/>
       <c r="E61" s="26">
         <v>2</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="66"/>
-      <c r="C62" s="92"/>
-      <c r="D62" s="92"/>
+      <c r="A62" s="68"/>
+      <c r="B62" s="70"/>
+      <c r="C62" s="74"/>
+      <c r="D62" s="74"/>
       <c r="E62" s="26">
         <v>3</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="66"/>
-      <c r="C63" s="92"/>
-      <c r="D63" s="92"/>
+      <c r="A63" s="69"/>
+      <c r="B63" s="70"/>
+      <c r="C63" s="74"/>
+      <c r="D63" s="74"/>
       <c r="E63" s="26">
         <v>4</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="32"/>
-      <c r="B64" s="86" t="s">
-        <v>337</v>
-      </c>
-      <c r="C64" s="87"/>
-      <c r="D64" s="88"/>
+      <c r="B64" s="71" t="s">
+        <v>338</v>
+      </c>
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
       <c r="E64" s="27"/>
       <c r="F64" s="33"/>
       <c r="G64" s="33"/>
@@ -4070,104 +4073,104 @@
       <c r="I64" s="33"/>
     </row>
     <row r="65" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B65" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" s="92" t="s">
+      <c r="A65" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D65" s="92" t="s">
+      <c r="C65" s="74" t="s">
         <v>96</v>
+      </c>
+      <c r="D65" s="74" t="s">
+        <v>97</v>
       </c>
       <c r="E65" s="26">
         <v>1</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="71"/>
-      <c r="B66" s="66"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
+      <c r="A66" s="68"/>
+      <c r="B66" s="70"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="74"/>
       <c r="E66" s="26">
         <v>2</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="71"/>
-      <c r="B67" s="66"/>
-      <c r="C67" s="92"/>
-      <c r="D67" s="92"/>
+      <c r="A67" s="68"/>
+      <c r="B67" s="70"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="74"/>
       <c r="E67" s="26">
         <v>3</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72"/>
-      <c r="B68" s="66"/>
-      <c r="C68" s="92"/>
-      <c r="D68" s="92"/>
+      <c r="A68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74"/>
       <c r="E68" s="26">
         <v>4</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32"/>
-      <c r="B69" s="86" t="s">
-        <v>338</v>
-      </c>
-      <c r="C69" s="87"/>
-      <c r="D69" s="88"/>
+      <c r="B69" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="C69" s="72"/>
+      <c r="D69" s="73"/>
       <c r="E69" s="27"/>
       <c r="F69" s="33"/>
       <c r="G69" s="33"/>
@@ -4175,100 +4178,100 @@
       <c r="I69" s="33"/>
     </row>
     <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="70" t="s">
-        <v>97</v>
-      </c>
-      <c r="B70" s="66" t="s">
+      <c r="A70" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="92" t="s">
+      <c r="B70" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D70" s="92" t="s">
+      <c r="C70" s="74" t="s">
         <v>100</v>
+      </c>
+      <c r="D70" s="74" t="s">
+        <v>101</v>
       </c>
       <c r="E70" s="26">
         <v>1</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="71"/>
-      <c r="B71" s="66"/>
-      <c r="C71" s="92"/>
-      <c r="D71" s="92"/>
+      <c r="A71" s="68"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
       <c r="E71" s="26">
         <v>2</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G71" s="24"/>
       <c r="H71" s="24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="71"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="92"/>
-      <c r="D72" s="92"/>
+      <c r="A72" s="68"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
       <c r="E72" s="26">
         <v>3</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G72" s="24"/>
       <c r="H72" s="24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="66"/>
-      <c r="C73" s="92"/>
-      <c r="D73" s="92"/>
+      <c r="A73" s="69"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="74"/>
+      <c r="D73" s="74"/>
       <c r="E73" s="26">
         <v>4</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32"/>
-      <c r="B74" s="86" t="s">
-        <v>339</v>
-      </c>
-      <c r="C74" s="87"/>
-      <c r="D74" s="88"/>
+      <c r="B74" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="C74" s="72"/>
+      <c r="D74" s="73"/>
       <c r="E74" s="27"/>
       <c r="F74" s="33"/>
       <c r="G74" s="33"/>
@@ -4276,104 +4279,104 @@
       <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="B75" s="66" t="s">
+      <c r="A75" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="C75" s="92" t="s">
+      <c r="B75" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="D75" s="92" t="s">
+      <c r="C75" s="74" t="s">
         <v>104</v>
+      </c>
+      <c r="D75" s="74" t="s">
+        <v>105</v>
       </c>
       <c r="E75" s="26">
         <v>1</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I75" s="24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="71"/>
-      <c r="B76" s="66"/>
-      <c r="C76" s="92"/>
-      <c r="D76" s="92"/>
+      <c r="A76" s="68"/>
+      <c r="B76" s="70"/>
+      <c r="C76" s="74"/>
+      <c r="D76" s="74"/>
       <c r="E76" s="26">
         <v>2</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I76" s="24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="71"/>
-      <c r="B77" s="66"/>
-      <c r="C77" s="92"/>
-      <c r="D77" s="92"/>
+      <c r="A77" s="68"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="74"/>
       <c r="E77" s="26">
         <v>3</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="92"/>
-      <c r="D78" s="92"/>
+      <c r="A78" s="69"/>
+      <c r="B78" s="70"/>
+      <c r="C78" s="74"/>
+      <c r="D78" s="74"/>
       <c r="E78" s="26">
         <v>4</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I78" s="24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="32"/>
-      <c r="B79" s="86" t="s">
-        <v>340</v>
-      </c>
-      <c r="C79" s="87"/>
-      <c r="D79" s="88"/>
+      <c r="B79" s="71" t="s">
+        <v>341</v>
+      </c>
+      <c r="C79" s="72"/>
+      <c r="D79" s="73"/>
       <c r="E79" s="27"/>
       <c r="F79" s="33"/>
       <c r="G79" s="33"/>
@@ -4381,104 +4384,104 @@
       <c r="I79" s="33"/>
     </row>
     <row r="80" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="70" t="s">
-        <v>105</v>
-      </c>
-      <c r="B80" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C80" s="92" t="s">
+      <c r="A80" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="D80" s="92" t="s">
+      <c r="B80" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C80" s="74" t="s">
         <v>107</v>
+      </c>
+      <c r="D80" s="74" t="s">
+        <v>108</v>
       </c>
       <c r="E80" s="26">
         <v>1</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I80" s="24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="71"/>
-      <c r="B81" s="66"/>
-      <c r="C81" s="92"/>
-      <c r="D81" s="92"/>
+      <c r="A81" s="68"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
       <c r="E81" s="26">
         <v>2</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I81" s="24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="71"/>
-      <c r="B82" s="66"/>
-      <c r="C82" s="92"/>
-      <c r="D82" s="92"/>
+      <c r="A82" s="68"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="74"/>
+      <c r="D82" s="74"/>
       <c r="E82" s="26">
         <v>3</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I82" s="24" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="92"/>
-      <c r="D83" s="92"/>
+      <c r="A83" s="69"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="74"/>
+      <c r="D83" s="74"/>
       <c r="E83" s="26">
         <v>4</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I83" s="24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="32"/>
-      <c r="B84" s="86" t="s">
-        <v>341</v>
-      </c>
-      <c r="C84" s="87"/>
-      <c r="D84" s="88"/>
+      <c r="B84" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C84" s="72"/>
+      <c r="D84" s="73"/>
       <c r="E84" s="27"/>
       <c r="F84" s="33"/>
       <c r="G84" s="33"/>
@@ -4486,99 +4489,165 @@
       <c r="I84" s="33"/>
     </row>
     <row r="85" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="70" t="s">
-        <v>108</v>
-      </c>
-      <c r="B85" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C85" s="92" t="s">
+      <c r="A85" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="D85" s="92" t="s">
+      <c r="B85" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" s="74" t="s">
         <v>110</v>
+      </c>
+      <c r="D85" s="74" t="s">
+        <v>111</v>
       </c>
       <c r="E85" s="26">
         <v>1</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I85" s="24" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="71"/>
-      <c r="B86" s="66"/>
-      <c r="C86" s="92"/>
-      <c r="D86" s="92"/>
+      <c r="A86" s="68"/>
+      <c r="B86" s="70"/>
+      <c r="C86" s="74"/>
+      <c r="D86" s="74"/>
       <c r="E86" s="26">
         <v>2</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="71"/>
-      <c r="B87" s="66"/>
-      <c r="C87" s="92"/>
-      <c r="D87" s="92"/>
+      <c r="A87" s="68"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="74"/>
+      <c r="D87" s="74"/>
       <c r="E87" s="26">
         <v>3</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I87" s="24" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="66"/>
-      <c r="C88" s="92"/>
-      <c r="D88" s="92"/>
+      <c r="A88" s="69"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="74"/>
+      <c r="D88" s="74"/>
       <c r="E88" s="26">
         <v>4</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="D9:D15"/>
+    <mergeCell ref="C9:C15"/>
+    <mergeCell ref="B9:B15"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="D65:D68"/>
+    <mergeCell ref="B65:B68"/>
     <mergeCell ref="A85:A88"/>
     <mergeCell ref="A80:A83"/>
     <mergeCell ref="A75:A78"/>
@@ -4595,72 +4664,6 @@
     <mergeCell ref="D80:D83"/>
     <mergeCell ref="D75:D78"/>
     <mergeCell ref="C85:C88"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="D17:D22"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="D9:D15"/>
-    <mergeCell ref="C9:C15"/>
-    <mergeCell ref="B9:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4685,55 +4688,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="78"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="101"/>
     </row>
     <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -4741,60 +4744,60 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="96" t="s">
-        <v>461</v>
-      </c>
-      <c r="C4" s="96" t="s">
+      <c r="A4" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="87" t="s">
         <v>462</v>
       </c>
-      <c r="D4" s="96" t="s">
+      <c r="C4" s="87" t="s">
         <v>463</v>
+      </c>
+      <c r="D4" s="87" t="s">
+        <v>464</v>
       </c>
       <c r="E4" s="40">
         <v>1</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
       <c r="E5" s="40">
         <v>2</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="79"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="40">
         <v>3</v>
       </c>
@@ -4804,10 +4807,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="79"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
       <c r="E7" s="40">
         <v>4</v>
       </c>
@@ -4818,11 +4821,11 @@
     </row>
     <row r="8" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
-      <c r="B8" s="103" t="s">
-        <v>327</v>
-      </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
+      <c r="B8" s="104" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -4830,60 +4833,60 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="96" t="s">
-        <v>464</v>
-      </c>
-      <c r="C9" s="96" t="s">
+      <c r="A9" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="87" t="s">
         <v>465</v>
       </c>
-      <c r="D9" s="96" t="s">
+      <c r="C9" s="87" t="s">
         <v>466</v>
+      </c>
+      <c r="D9" s="87" t="s">
+        <v>467</v>
       </c>
       <c r="E9" s="40">
         <v>1</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="79"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="34">
         <v>2</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="79"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
       <c r="E11" s="40">
         <v>3</v>
       </c>
@@ -4893,10 +4896,10 @@
       <c r="I11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
+      <c r="A12" s="81"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
       <c r="E12" s="40">
         <v>4</v>
       </c>
@@ -4907,11 +4910,11 @@
     </row>
     <row r="13" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35"/>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="35"/>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
@@ -4919,81 +4922,81 @@
       <c r="I13" s="36"/>
     </row>
     <row r="14" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="96" t="s">
-        <v>467</v>
-      </c>
-      <c r="C14" s="96" t="s">
+      <c r="A14" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="87" t="s">
         <v>468</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="C14" s="87" t="s">
         <v>469</v>
+      </c>
+      <c r="D14" s="87" t="s">
+        <v>470</v>
       </c>
       <c r="E14" s="40">
         <v>1</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="97"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
       <c r="E15" s="40">
         <v>2</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="40">
         <v>3</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="79"/>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
+      <c r="A17" s="81"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
       <c r="E17" s="40">
         <v>4</v>
       </c>
@@ -5004,11 +5007,11 @@
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
       <c r="E18" s="35"/>
       <c r="F18" s="36"/>
       <c r="G18" s="36"/>
@@ -5016,81 +5019,81 @@
       <c r="I18" s="36"/>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="96" t="s">
-        <v>467</v>
-      </c>
-      <c r="C19" s="96" t="s">
-        <v>470</v>
-      </c>
-      <c r="D19" s="96" t="s">
+      <c r="A19" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="87" t="s">
+        <v>468</v>
+      </c>
+      <c r="C19" s="87" t="s">
         <v>471</v>
+      </c>
+      <c r="D19" s="87" t="s">
+        <v>472</v>
       </c>
       <c r="E19" s="40">
         <v>1</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H19" s="41" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="40">
         <v>2</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G20" s="41" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="79"/>
-      <c r="B21" s="97"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
       <c r="E21" s="40">
         <v>3</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="79"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
       <c r="E22" s="40">
         <v>4</v>
       </c>
@@ -5101,11 +5104,11 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="102"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
       <c r="E23" s="35"/>
       <c r="F23" s="36"/>
       <c r="G23" s="36"/>
@@ -5113,141 +5116,154 @@
       <c r="I23" s="36"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="83" t="s">
-        <v>472</v>
-      </c>
-      <c r="C24" s="83" t="s">
+      <c r="A24" s="84" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="84" t="s">
         <v>473</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="C24" s="84" t="s">
         <v>474</v>
+      </c>
+      <c r="D24" s="84" t="s">
+        <v>475</v>
       </c>
       <c r="E24" s="40">
         <v>1</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G24" s="41" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H24" s="41" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I24" s="41" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="40">
         <v>2</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G25" s="41" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I25" s="41" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
       <c r="E26" s="40">
         <v>3</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="40">
         <v>4</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I27" s="41" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
       <c r="E28" s="40">
         <v>5</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
+      <c r="A29" s="86"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
       <c r="E29" s="40">
         <v>6</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
     <mergeCell ref="D24:D29"/>
     <mergeCell ref="C24:C29"/>
     <mergeCell ref="B24:B29"/>
@@ -5262,19 +5278,6 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5283,7 +5286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BBA4C7C-1B75-4CC3-9108-DB4740564B4D}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="11" customWidth="1"/>
@@ -5306,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -5324,24 +5327,24 @@
         <v>6</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="53" t="s">
         <v>26</v>
@@ -5356,103 +5359,73 @@
         <v>31</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>356</v>
-      </c>
+      <c r="A3" s="10"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="54" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>357</v>
+        <v>565</v>
       </c>
       <c r="F3" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="53"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+    </row>
+    <row r="4" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="54" t="s">
+        <v>332</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+    </row>
+    <row r="5" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="53" t="s">
         <v>358</v>
       </c>
-      <c r="I3" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" s="54" t="s">
-        <v>564</v>
+        <v>27</v>
       </c>
       <c r="G5" s="53" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>565</v>
+        <v>359</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J5" s="39" t="s">
         <v>39</v>
@@ -5460,259 +5433,263 @@
     </row>
     <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>398</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>368</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>373</v>
+        <v>367</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>385</v>
-      </c>
-      <c r="G6" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="I6" s="39" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="J6" s="39" t="s">
-        <v>383</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>399</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>369</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>374</v>
+        <v>368</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>386</v>
-      </c>
-      <c r="G7" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="I7" s="39" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>382</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>393</v>
+        <v>30</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="39" t="s">
-        <v>379</v>
-      </c>
-      <c r="J8" s="52" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>393</v>
+        <v>30</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="J9" s="52" t="s">
-        <v>382</v>
+        <v>379</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E10" s="39" t="s">
         <v>376</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="39" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="39" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>66</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F12" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="39" t="s">
         <v>382</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>97</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F13" s="54" t="s">
         <v>390</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>30</v>
+        <v>394</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F14" s="54" t="s">
         <v>391</v>
@@ -5722,40 +5699,100 @@
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>404</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F15" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G15" s="39" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>108</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>392</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>405</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5790,112 +5827,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="106" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="107"/>
-      <c r="J1" s="106" t="s">
-        <v>345</v>
-      </c>
-      <c r="K1" s="107"/>
-      <c r="M1" s="106" t="s">
+      <c r="G1" s="107" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="108"/>
+      <c r="J1" s="107" t="s">
         <v>346</v>
       </c>
-      <c r="N1" s="107"/>
-      <c r="P1" s="106" t="s">
+      <c r="K1" s="108"/>
+      <c r="M1" s="107" t="s">
         <v>347</v>
       </c>
-      <c r="Q1" s="107"/>
-      <c r="S1" s="106" t="s">
+      <c r="N1" s="108"/>
+      <c r="P1" s="107" t="s">
         <v>348</v>
       </c>
-      <c r="T1" s="107"/>
-      <c r="V1" s="106" t="s">
+      <c r="Q1" s="108"/>
+      <c r="S1" s="107" t="s">
         <v>349</v>
       </c>
-      <c r="W1" s="107"/>
-      <c r="Y1" s="106" t="s">
+      <c r="T1" s="108"/>
+      <c r="V1" s="107" t="s">
         <v>350</v>
       </c>
-      <c r="Z1" s="107"/>
+      <c r="W1" s="108"/>
+      <c r="Y1" s="107" t="s">
+        <v>351</v>
+      </c>
+      <c r="Z1" s="108"/>
     </row>
     <row r="2" spans="1:31" s="17" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" s="12"/>
       <c r="V2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X2" s="12"/>
       <c r="Y2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB2" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>7</v>
@@ -5907,7 +5944,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -5974,7 +6011,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
@@ -6041,7 +6078,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
@@ -6108,7 +6145,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -6168,19 +6205,19 @@
     </row>
     <row r="7" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D7" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="14"/>
@@ -6210,13 +6247,13 @@
       <c r="A8" s="2"/>
       <c r="B8" s="57"/>
       <c r="C8" s="50" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D8" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="14"/>
@@ -6246,13 +6283,13 @@
       <c r="A9" s="2"/>
       <c r="B9" s="57"/>
       <c r="C9" s="50" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D9" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="14"/>
@@ -6282,13 +6319,13 @@
       <c r="A10" s="2"/>
       <c r="B10" s="57"/>
       <c r="C10" s="50" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D10" s="54" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="14"/>
@@ -6316,7 +6353,7 @@
     </row>
     <row r="11" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B11" s="56" t="s">
         <v>8</v>
@@ -6328,7 +6365,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="14"/>
@@ -6391,7 +6428,7 @@
         <v>28</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="14"/>
@@ -6454,7 +6491,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="14"/>
@@ -6517,7 +6554,7 @@
         <v>28</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="14"/>
@@ -6572,7 +6609,7 @@
     </row>
     <row r="15" spans="1:31" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B15" s="56" t="s">
         <v>9</v>
@@ -6584,7 +6621,7 @@
         <v>29</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="14"/>
@@ -6647,7 +6684,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="14"/>
@@ -6710,7 +6747,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="14"/>
@@ -6773,7 +6810,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="14"/>
@@ -6836,7 +6873,7 @@
         <v>29</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="38"/>
@@ -6881,7 +6918,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="38"/>
@@ -6926,7 +6963,7 @@
         <v>29</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="38"/>
@@ -6971,7 +7008,7 @@
         <v>29</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="38"/>
@@ -7008,19 +7045,19 @@
     </row>
     <row r="23" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="38"/>
@@ -7059,13 +7096,13 @@
       <c r="A24" s="2"/>
       <c r="B24" s="58"/>
       <c r="C24" s="52" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="38"/>
@@ -7098,13 +7135,13 @@
       <c r="A25" s="2"/>
       <c r="B25" s="58"/>
       <c r="C25" s="52" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="38"/>
@@ -7137,13 +7174,13 @@
       <c r="A26" s="2"/>
       <c r="B26" s="58"/>
       <c r="C26" s="52" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="38"/>
@@ -7176,13 +7213,13 @@
       <c r="A27" s="2"/>
       <c r="B27" s="58"/>
       <c r="C27" s="52" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D27" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="38"/>
@@ -7215,13 +7252,13 @@
       <c r="A28" s="2"/>
       <c r="B28" s="58"/>
       <c r="C28" s="52" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D28" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="38"/>
@@ -7254,13 +7291,13 @@
       <c r="A29" s="4"/>
       <c r="B29" s="58"/>
       <c r="C29" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D29" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="38"/>
@@ -7299,13 +7336,13 @@
       <c r="A30" s="4"/>
       <c r="B30" s="58"/>
       <c r="C30" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D30" s="54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="38"/>
@@ -7342,19 +7379,19 @@
     </row>
     <row r="31" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B31" s="58" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D31" s="54" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="38"/>
@@ -7393,13 +7430,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="58"/>
       <c r="C32" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="38"/>
@@ -7438,13 +7475,13 @@
       <c r="A33" s="2"/>
       <c r="B33" s="58"/>
       <c r="C33" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D33" s="54" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E33" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="38"/>
@@ -7481,19 +7518,19 @@
     </row>
     <row r="34" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="38"/>
@@ -7531,13 +7568,13 @@
     <row r="35" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="58"/>
       <c r="C35" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="38"/>
@@ -7575,13 +7612,13 @@
     <row r="36" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="58"/>
       <c r="C36" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="38"/>
@@ -7618,19 +7655,19 @@
     </row>
     <row r="37" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B37" s="58" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="38"/>
@@ -7669,13 +7706,13 @@
       <c r="A38" s="2"/>
       <c r="B38" s="58"/>
       <c r="C38" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="38"/>
@@ -7714,13 +7751,13 @@
       <c r="A39" s="2"/>
       <c r="B39" s="58"/>
       <c r="C39" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="38"/>
@@ -7759,13 +7796,13 @@
       <c r="A40" s="2"/>
       <c r="B40" s="58"/>
       <c r="C40" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="38"/>
@@ -7802,19 +7839,19 @@
     </row>
     <row r="41" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B41" s="58" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="38"/>
@@ -7852,13 +7889,13 @@
     <row r="42" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="58"/>
       <c r="C42" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="38"/>
@@ -7896,13 +7933,13 @@
     <row r="43" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="58"/>
       <c r="C43" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D43" s="54" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E43" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="38"/>
@@ -7939,19 +7976,19 @@
     </row>
     <row r="44" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="38"/>
@@ -7990,13 +8027,13 @@
       <c r="A45" s="2"/>
       <c r="B45" s="58"/>
       <c r="C45" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D45" s="54" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="38"/>
@@ -8035,13 +8072,13 @@
       <c r="A46" s="2"/>
       <c r="B46" s="58"/>
       <c r="C46" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D46" s="54" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="38"/>
@@ -8078,19 +8115,19 @@
     </row>
     <row r="47" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B47" s="58" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="38"/>
@@ -8129,13 +8166,13 @@
       <c r="A48" s="48"/>
       <c r="B48" s="58"/>
       <c r="C48" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D48" s="54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="38"/>
@@ -8167,13 +8204,13 @@
     <row r="49" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="58"/>
       <c r="C49" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E49" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="38"/>
@@ -8211,13 +8248,13 @@
     <row r="50" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="58"/>
       <c r="C50" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D50" s="54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="38"/>
@@ -8249,13 +8286,13 @@
     <row r="51" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="58"/>
       <c r="C51" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D51" s="54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E51" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="38"/>
@@ -8292,19 +8329,19 @@
     </row>
     <row r="52" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E52" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="38"/>
@@ -8343,13 +8380,13 @@
       <c r="A53" s="2"/>
       <c r="B53" s="58"/>
       <c r="C53" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D53" s="54" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E53" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="38"/>
@@ -8388,13 +8425,13 @@
       <c r="A54" s="2"/>
       <c r="B54" s="58"/>
       <c r="C54" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D54" s="54" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="38"/>
@@ -8431,19 +8468,19 @@
     </row>
     <row r="55" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="38"/>
@@ -8481,13 +8518,13 @@
     <row r="56" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="58"/>
       <c r="C56" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D56" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="38"/>
@@ -8526,13 +8563,13 @@
       <c r="A57" s="2"/>
       <c r="B57" s="58"/>
       <c r="C57" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E57" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="38"/>
@@ -8569,19 +8606,19 @@
     </row>
     <row r="58" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D58" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="38"/>
@@ -8620,13 +8657,13 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D59" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E59" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="38"/>
@@ -8665,13 +8702,13 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D60" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E60" s="39" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="38"/>

--- a/Documents/HU, HT, PB, SB.xlsx
+++ b/Documents/HU, HT, PB, SB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8397588-E4C4-45ED-874D-5417E68B970B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B847C3-5FA9-4B61-8A34-2D7110580CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="3" xr2:uid="{D7927580-9A21-4766-84F0-58BE9C7E4DF7}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="568">
   <si>
     <t>Identificador (ID) de la Historia</t>
   </si>
@@ -1736,6 +1736,12 @@
   </si>
   <si>
     <t>2 dias</t>
+  </si>
+  <si>
+    <t>4 dias</t>
+  </si>
+  <si>
+    <t>Ht4</t>
   </si>
 </sst>
 </file>
@@ -2158,7 +2164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2348,6 +2354,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2357,20 +2375,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2381,33 +2447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2426,36 +2465,6 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2473,6 +2482,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2814,18 +2826,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="101"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -2858,11 +2870,11 @@
     </row>
     <row r="3" spans="1:9" s="37" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -2870,16 +2882,16 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="82" t="s">
         <v>70</v>
       </c>
       <c r="E4" s="26">
@@ -2899,10 +2911,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="83"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="26">
         <v>2</v>
       </c>
@@ -2918,10 +2930,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="81"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="83"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="82"/>
       <c r="E6" s="26">
         <v>3</v>
       </c>
@@ -2937,10 +2949,10 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="81"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="83"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
       <c r="E7" s="26">
         <v>4</v>
       </c>
@@ -2959,11 +2971,11 @@
     </row>
     <row r="8" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31"/>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="84" t="s">
         <v>330</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="80"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="86"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -2971,16 +2983,16 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="90" t="s">
         <v>77</v>
       </c>
       <c r="E9" s="26">
@@ -2998,10 +3010,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
       <c r="E10" s="26">
         <v>2</v>
       </c>
@@ -3019,10 +3031,10 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="68"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
       <c r="E11" s="26">
         <v>3</v>
       </c>
@@ -3040,10 +3052,10 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="68"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
       <c r="E12" s="43"/>
       <c r="F12" s="23" t="s">
         <v>547</v>
@@ -3053,10 +3065,10 @@
       <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="68"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
       <c r="E13" s="43"/>
       <c r="F13" s="61" t="s">
         <v>548</v>
@@ -3066,10 +3078,10 @@
       <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="68"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
       <c r="E14" s="43"/>
       <c r="F14" s="44" t="s">
         <v>549</v>
@@ -3079,10 +3091,10 @@
       <c r="I14" s="44"/>
     </row>
     <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="69"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
       <c r="E15" s="26">
         <v>4</v>
       </c>
@@ -3101,11 +3113,11 @@
     </row>
     <row r="16" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="73"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="27"/>
       <c r="F16" s="62"/>
       <c r="G16" s="28"/>
@@ -3113,16 +3125,16 @@
       <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="91" t="s">
         <v>81</v>
       </c>
       <c r="E17" s="26">
@@ -3142,10 +3154,10 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="70"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="91"/>
       <c r="E18" s="26">
         <v>2</v>
       </c>
@@ -3161,10 +3173,10 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="68"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="70"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="43"/>
       <c r="F19" s="44" t="s">
         <v>553</v>
@@ -3174,10 +3186,10 @@
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68"/>
-      <c r="B20" s="70"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="70"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="26">
         <v>3</v>
       </c>
@@ -3195,10 +3207,10 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="68"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="70"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="26">
         <v>4</v>
       </c>
@@ -3216,10 +3228,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="69"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="70"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="97"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="43"/>
       <c r="F22" s="44" t="s">
         <v>556</v>
@@ -3230,11 +3242,11 @@
     </row>
     <row r="23" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="84" t="s">
         <v>328</v>
       </c>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="86"/>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
@@ -3242,16 +3254,16 @@
       <c r="I23" s="28"/>
     </row>
     <row r="24" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="81" t="s">
+      <c r="A24" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="82" t="s">
+      <c r="C24" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="D24" s="82" t="s">
         <v>73</v>
       </c>
       <c r="E24" s="26">
@@ -3269,10 +3281,10 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="81"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="82"/>
       <c r="E25" s="34">
         <v>2</v>
       </c>
@@ -3288,10 +3300,10 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="81"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="83"/>
+      <c r="A26" s="80"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="82"/>
       <c r="E26" s="26">
         <v>3</v>
       </c>
@@ -3307,10 +3319,10 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="81"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="80"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="82"/>
       <c r="E27" s="26">
         <v>4</v>
       </c>
@@ -3329,11 +3341,11 @@
     </row>
     <row r="28" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30"/>
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="84" t="s">
         <v>329</v>
       </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="86"/>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
@@ -3341,16 +3353,16 @@
       <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84" t="s">
+      <c r="A29" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="84" t="s">
+      <c r="B29" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="87" t="s">
+      <c r="C29" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="90" t="s">
+      <c r="D29" s="101" t="s">
         <v>75</v>
       </c>
       <c r="E29" s="26">
@@ -3368,10 +3380,10 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="91"/>
+      <c r="A30" s="93"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="102"/>
       <c r="E30" s="26">
         <v>2</v>
       </c>
@@ -3387,10 +3399,10 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="91"/>
+      <c r="A31" s="93"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="102"/>
       <c r="E31" s="26">
         <v>3</v>
       </c>
@@ -3408,10 +3420,10 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="92"/>
+      <c r="A32" s="94"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="103"/>
       <c r="E32" s="26">
         <v>4</v>
       </c>
@@ -3430,11 +3442,11 @@
     </row>
     <row r="33" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
-      <c r="B33" s="71" t="s">
+      <c r="B33" s="87" t="s">
         <v>331</v>
       </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="73"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
@@ -3442,16 +3454,16 @@
       <c r="I33" s="28"/>
     </row>
     <row r="34" spans="1:9" s="64" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="93" t="s">
+      <c r="D34" s="68" t="s">
         <v>79</v>
       </c>
       <c r="E34" s="34"/>
@@ -3463,10 +3475,10 @@
       <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="68"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="94"/>
+      <c r="A35" s="72"/>
+      <c r="B35" s="91"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="69"/>
       <c r="E35" s="26">
         <v>1</v>
       </c>
@@ -3482,10 +3494,10 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="68"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="94"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="69"/>
       <c r="E36" s="26">
         <v>2</v>
       </c>
@@ -3501,10 +3513,10 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="68"/>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="94"/>
+      <c r="A37" s="72"/>
+      <c r="B37" s="91"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="69"/>
       <c r="E37" s="26">
         <v>3</v>
       </c>
@@ -3522,10 +3534,10 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="69"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="95"/>
+      <c r="A38" s="73"/>
+      <c r="B38" s="91"/>
+      <c r="C38" s="91"/>
+      <c r="D38" s="70"/>
       <c r="E38" s="26">
         <v>4</v>
       </c>
@@ -3544,11 +3556,11 @@
     </row>
     <row r="39" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="87" t="s">
         <v>333</v>
       </c>
-      <c r="C39" s="72"/>
-      <c r="D39" s="73"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="89"/>
       <c r="E39" s="27"/>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
@@ -3556,16 +3568,16 @@
       <c r="I39" s="28"/>
     </row>
     <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="70" t="s">
+      <c r="B40" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="D40" s="74" t="s">
+      <c r="D40" s="90" t="s">
         <v>84</v>
       </c>
       <c r="E40" s="26">
@@ -3583,10 +3595,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="68"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
+      <c r="A41" s="72"/>
+      <c r="B41" s="91"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
       <c r="E41" s="26">
         <v>2</v>
       </c>
@@ -3602,10 +3614,10 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="68"/>
-      <c r="B42" s="70"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
+      <c r="A42" s="72"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
       <c r="E42" s="26">
         <v>3</v>
       </c>
@@ -3623,10 +3635,10 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="69"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
+      <c r="A43" s="73"/>
+      <c r="B43" s="91"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="90"/>
       <c r="E43" s="26">
         <v>4</v>
       </c>
@@ -3645,11 +3657,11 @@
     </row>
     <row r="44" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
-      <c r="B44" s="71" t="s">
+      <c r="B44" s="87" t="s">
         <v>334</v>
       </c>
-      <c r="C44" s="72"/>
-      <c r="D44" s="73"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="89"/>
       <c r="E44" s="27"/>
       <c r="F44" s="33"/>
       <c r="G44" s="33"/>
@@ -3657,16 +3669,16 @@
       <c r="I44" s="33"/>
     </row>
     <row r="45" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="67" t="s">
+      <c r="A45" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="70" t="s">
+      <c r="B45" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="C45" s="74" t="s">
+      <c r="C45" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="74" t="s">
+      <c r="D45" s="90" t="s">
         <v>86</v>
       </c>
       <c r="E45" s="26">
@@ -3686,10 +3698,10 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="68"/>
-      <c r="B46" s="70"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
+      <c r="A46" s="72"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="90"/>
       <c r="E46" s="26">
         <v>2</v>
       </c>
@@ -3707,10 +3719,10 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="68"/>
-      <c r="B47" s="70"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
+      <c r="A47" s="72"/>
+      <c r="B47" s="91"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
       <c r="E47" s="26">
         <v>3</v>
       </c>
@@ -3728,10 +3740,10 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="69"/>
-      <c r="B48" s="70"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="90"/>
       <c r="E48" s="26">
         <v>4</v>
       </c>
@@ -3750,11 +3762,11 @@
     </row>
     <row r="49" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32"/>
-      <c r="B49" s="71" t="s">
+      <c r="B49" s="87" t="s">
         <v>335</v>
       </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="73"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="89"/>
       <c r="E49" s="27"/>
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
@@ -3762,16 +3774,16 @@
       <c r="I49" s="33"/>
     </row>
     <row r="50" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="91" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="74" t="s">
+      <c r="C50" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="74" t="s">
+      <c r="D50" s="90" t="s">
         <v>89</v>
       </c>
       <c r="E50" s="26">
@@ -3791,10 +3803,10 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="68"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="74"/>
-      <c r="D51" s="74"/>
+      <c r="A51" s="72"/>
+      <c r="B51" s="91"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
       <c r="E51" s="26">
         <v>2</v>
       </c>
@@ -3810,10 +3822,10 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="68"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
+      <c r="A52" s="72"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="90"/>
       <c r="E52" s="26">
         <v>3</v>
       </c>
@@ -3831,10 +3843,10 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="69"/>
-      <c r="B53" s="70"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
+      <c r="A53" s="73"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="90"/>
       <c r="E53" s="26">
         <v>4</v>
       </c>
@@ -3853,11 +3865,11 @@
     </row>
     <row r="54" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="32"/>
-      <c r="B54" s="71" t="s">
+      <c r="B54" s="87" t="s">
         <v>336</v>
       </c>
-      <c r="C54" s="72"/>
-      <c r="D54" s="73"/>
+      <c r="C54" s="88"/>
+      <c r="D54" s="89"/>
       <c r="E54" s="27"/>
       <c r="F54" s="33"/>
       <c r="G54" s="33"/>
@@ -3865,16 +3877,16 @@
       <c r="I54" s="33"/>
     </row>
     <row r="55" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="70" t="s">
+      <c r="B55" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="74" t="s">
+      <c r="C55" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="74" t="s">
+      <c r="D55" s="90" t="s">
         <v>92</v>
       </c>
       <c r="E55" s="26">
@@ -3894,10 +3906,10 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="68"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
+      <c r="A56" s="72"/>
+      <c r="B56" s="91"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="90"/>
       <c r="E56" s="26">
         <v>2</v>
       </c>
@@ -3915,10 +3927,10 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="68"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
+      <c r="A57" s="72"/>
+      <c r="B57" s="91"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="90"/>
       <c r="E57" s="26">
         <v>3</v>
       </c>
@@ -3936,10 +3948,10 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="69"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
+      <c r="A58" s="73"/>
+      <c r="B58" s="91"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="90"/>
       <c r="E58" s="26">
         <v>4</v>
       </c>
@@ -3958,11 +3970,11 @@
     </row>
     <row r="59" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="32"/>
-      <c r="B59" s="71" t="s">
+      <c r="B59" s="87" t="s">
         <v>337</v>
       </c>
-      <c r="C59" s="72"/>
-      <c r="D59" s="73"/>
+      <c r="C59" s="88"/>
+      <c r="D59" s="89"/>
       <c r="E59" s="27"/>
       <c r="F59" s="33"/>
       <c r="G59" s="33"/>
@@ -3970,16 +3982,16 @@
       <c r="I59" s="33"/>
     </row>
     <row r="60" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="70" t="s">
+      <c r="B60" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="74" t="s">
+      <c r="C60" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="74" t="s">
+      <c r="D60" s="90" t="s">
         <v>94</v>
       </c>
       <c r="E60" s="26">
@@ -3997,10 +4009,10 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="68"/>
-      <c r="B61" s="70"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="74"/>
+      <c r="A61" s="72"/>
+      <c r="B61" s="91"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="90"/>
       <c r="E61" s="26">
         <v>2</v>
       </c>
@@ -4018,10 +4030,10 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="68"/>
-      <c r="B62" s="70"/>
-      <c r="C62" s="74"/>
-      <c r="D62" s="74"/>
+      <c r="A62" s="72"/>
+      <c r="B62" s="91"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="90"/>
       <c r="E62" s="26">
         <v>3</v>
       </c>
@@ -4039,10 +4051,10 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="69"/>
-      <c r="B63" s="70"/>
-      <c r="C63" s="74"/>
-      <c r="D63" s="74"/>
+      <c r="A63" s="73"/>
+      <c r="B63" s="91"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="90"/>
       <c r="E63" s="26">
         <v>4</v>
       </c>
@@ -4061,11 +4073,11 @@
     </row>
     <row r="64" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="32"/>
-      <c r="B64" s="71" t="s">
+      <c r="B64" s="87" t="s">
         <v>338</v>
       </c>
-      <c r="C64" s="72"/>
-      <c r="D64" s="73"/>
+      <c r="C64" s="88"/>
+      <c r="D64" s="89"/>
       <c r="E64" s="27"/>
       <c r="F64" s="33"/>
       <c r="G64" s="33"/>
@@ -4073,16 +4085,16 @@
       <c r="I64" s="33"/>
     </row>
     <row r="65" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="67" t="s">
+      <c r="A65" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="70" t="s">
+      <c r="B65" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="C65" s="74" t="s">
+      <c r="C65" s="90" t="s">
         <v>96</v>
       </c>
-      <c r="D65" s="74" t="s">
+      <c r="D65" s="90" t="s">
         <v>97</v>
       </c>
       <c r="E65" s="26">
@@ -4102,10 +4114,10 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="68"/>
-      <c r="B66" s="70"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="74"/>
+      <c r="A66" s="72"/>
+      <c r="B66" s="91"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
       <c r="E66" s="26">
         <v>2</v>
       </c>
@@ -4123,10 +4135,10 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="68"/>
-      <c r="B67" s="70"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="74"/>
+      <c r="A67" s="72"/>
+      <c r="B67" s="91"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="90"/>
       <c r="E67" s="26">
         <v>3</v>
       </c>
@@ -4144,10 +4156,10 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="69"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
+      <c r="A68" s="73"/>
+      <c r="B68" s="91"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="90"/>
       <c r="E68" s="26">
         <v>4</v>
       </c>
@@ -4166,11 +4178,11 @@
     </row>
     <row r="69" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32"/>
-      <c r="B69" s="71" t="s">
+      <c r="B69" s="87" t="s">
         <v>339</v>
       </c>
-      <c r="C69" s="72"/>
-      <c r="D69" s="73"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="89"/>
       <c r="E69" s="27"/>
       <c r="F69" s="33"/>
       <c r="G69" s="33"/>
@@ -4178,16 +4190,16 @@
       <c r="I69" s="33"/>
     </row>
     <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="67" t="s">
+      <c r="A70" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="70" t="s">
+      <c r="B70" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="74" t="s">
+      <c r="C70" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="D70" s="74" t="s">
+      <c r="D70" s="90" t="s">
         <v>101</v>
       </c>
       <c r="E70" s="26">
@@ -4207,10 +4219,10 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="68"/>
-      <c r="B71" s="70"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
+      <c r="A71" s="72"/>
+      <c r="B71" s="91"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="90"/>
       <c r="E71" s="26">
         <v>2</v>
       </c>
@@ -4226,10 +4238,10 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="68"/>
-      <c r="B72" s="70"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
+      <c r="A72" s="72"/>
+      <c r="B72" s="91"/>
+      <c r="C72" s="90"/>
+      <c r="D72" s="90"/>
       <c r="E72" s="26">
         <v>3</v>
       </c>
@@ -4245,10 +4257,10 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="69"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="74"/>
-      <c r="D73" s="74"/>
+      <c r="A73" s="73"/>
+      <c r="B73" s="91"/>
+      <c r="C73" s="90"/>
+      <c r="D73" s="90"/>
       <c r="E73" s="26">
         <v>4</v>
       </c>
@@ -4267,11 +4279,11 @@
     </row>
     <row r="74" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32"/>
-      <c r="B74" s="71" t="s">
+      <c r="B74" s="87" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="72"/>
-      <c r="D74" s="73"/>
+      <c r="C74" s="88"/>
+      <c r="D74" s="89"/>
       <c r="E74" s="27"/>
       <c r="F74" s="33"/>
       <c r="G74" s="33"/>
@@ -4279,16 +4291,16 @@
       <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="67" t="s">
+      <c r="A75" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="B75" s="70" t="s">
+      <c r="B75" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="74" t="s">
+      <c r="C75" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="D75" s="74" t="s">
+      <c r="D75" s="90" t="s">
         <v>105</v>
       </c>
       <c r="E75" s="26">
@@ -4308,10 +4320,10 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="68"/>
-      <c r="B76" s="70"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
+      <c r="A76" s="72"/>
+      <c r="B76" s="91"/>
+      <c r="C76" s="90"/>
+      <c r="D76" s="90"/>
       <c r="E76" s="26">
         <v>2</v>
       </c>
@@ -4329,10 +4341,10 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="68"/>
-      <c r="B77" s="70"/>
-      <c r="C77" s="74"/>
-      <c r="D77" s="74"/>
+      <c r="A77" s="72"/>
+      <c r="B77" s="91"/>
+      <c r="C77" s="90"/>
+      <c r="D77" s="90"/>
       <c r="E77" s="26">
         <v>3</v>
       </c>
@@ -4350,10 +4362,10 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="69"/>
-      <c r="B78" s="70"/>
-      <c r="C78" s="74"/>
-      <c r="D78" s="74"/>
+      <c r="A78" s="73"/>
+      <c r="B78" s="91"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="90"/>
       <c r="E78" s="26">
         <v>4</v>
       </c>
@@ -4372,11 +4384,11 @@
     </row>
     <row r="79" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="32"/>
-      <c r="B79" s="71" t="s">
+      <c r="B79" s="87" t="s">
         <v>341</v>
       </c>
-      <c r="C79" s="72"/>
-      <c r="D79" s="73"/>
+      <c r="C79" s="88"/>
+      <c r="D79" s="89"/>
       <c r="E79" s="27"/>
       <c r="F79" s="33"/>
       <c r="G79" s="33"/>
@@ -4384,16 +4396,16 @@
       <c r="I79" s="33"/>
     </row>
     <row r="80" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="70" t="s">
+      <c r="B80" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C80" s="74" t="s">
+      <c r="C80" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="D80" s="74" t="s">
+      <c r="D80" s="90" t="s">
         <v>108</v>
       </c>
       <c r="E80" s="26">
@@ -4413,10 +4425,10 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="68"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
+      <c r="A81" s="72"/>
+      <c r="B81" s="91"/>
+      <c r="C81" s="90"/>
+      <c r="D81" s="90"/>
       <c r="E81" s="26">
         <v>2</v>
       </c>
@@ -4434,10 +4446,10 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="68"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="74"/>
-      <c r="D82" s="74"/>
+      <c r="A82" s="72"/>
+      <c r="B82" s="91"/>
+      <c r="C82" s="90"/>
+      <c r="D82" s="90"/>
       <c r="E82" s="26">
         <v>3</v>
       </c>
@@ -4455,10 +4467,10 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="69"/>
-      <c r="B83" s="70"/>
-      <c r="C83" s="74"/>
-      <c r="D83" s="74"/>
+      <c r="A83" s="73"/>
+      <c r="B83" s="91"/>
+      <c r="C83" s="90"/>
+      <c r="D83" s="90"/>
       <c r="E83" s="26">
         <v>4</v>
       </c>
@@ -4477,11 +4489,11 @@
     </row>
     <row r="84" spans="1:9" s="29" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="32"/>
-      <c r="B84" s="71" t="s">
+      <c r="B84" s="87" t="s">
         <v>342</v>
       </c>
-      <c r="C84" s="72"/>
-      <c r="D84" s="73"/>
+      <c r="C84" s="88"/>
+      <c r="D84" s="89"/>
       <c r="E84" s="27"/>
       <c r="F84" s="33"/>
       <c r="G84" s="33"/>
@@ -4489,16 +4501,16 @@
       <c r="I84" s="33"/>
     </row>
     <row r="85" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="67" t="s">
+      <c r="A85" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="B85" s="70" t="s">
+      <c r="B85" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="C85" s="74" t="s">
+      <c r="C85" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="D85" s="74" t="s">
+      <c r="D85" s="90" t="s">
         <v>111</v>
       </c>
       <c r="E85" s="26">
@@ -4518,10 +4530,10 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="68"/>
-      <c r="B86" s="70"/>
-      <c r="C86" s="74"/>
-      <c r="D86" s="74"/>
+      <c r="A86" s="72"/>
+      <c r="B86" s="91"/>
+      <c r="C86" s="90"/>
+      <c r="D86" s="90"/>
       <c r="E86" s="26">
         <v>2</v>
       </c>
@@ -4539,10 +4551,10 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="68"/>
-      <c r="B87" s="70"/>
-      <c r="C87" s="74"/>
-      <c r="D87" s="74"/>
+      <c r="A87" s="72"/>
+      <c r="B87" s="91"/>
+      <c r="C87" s="90"/>
+      <c r="D87" s="90"/>
       <c r="E87" s="26">
         <v>3</v>
       </c>
@@ -4560,10 +4572,10 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="69"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="74"/>
-      <c r="D88" s="74"/>
+      <c r="A88" s="73"/>
+      <c r="B88" s="91"/>
+      <c r="C88" s="90"/>
+      <c r="D88" s="90"/>
       <c r="E88" s="26">
         <v>4</v>
       </c>
@@ -4582,26 +4594,52 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="D9:D15"/>
-    <mergeCell ref="C9:C15"/>
-    <mergeCell ref="B9:B15"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="D65:D68"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="C60:C63"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="C17:C22"/>
@@ -4618,52 +4656,26 @@
     <mergeCell ref="D29:D32"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="C34:C38"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="A85:A88"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="D85:D88"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="D75:D78"/>
-    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="D9:D15"/>
+    <mergeCell ref="C9:C15"/>
+    <mergeCell ref="B9:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4688,18 +4700,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="101"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -4732,11 +4744,11 @@
     </row>
     <row r="3" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
@@ -4744,16 +4756,16 @@
       <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="98" t="s">
         <v>462</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="98" t="s">
         <v>463</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="98" t="s">
         <v>464</v>
       </c>
       <c r="E4" s="40">
@@ -4773,10 +4785,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
       <c r="E5" s="40">
         <v>2</v>
       </c>
@@ -4794,10 +4806,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="81"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
       <c r="E6" s="40">
         <v>3</v>
       </c>
@@ -4807,10 +4819,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="81"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
       <c r="E7" s="40">
         <v>4</v>
       </c>
@@ -4821,11 +4833,11 @@
     </row>
     <row r="8" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="105" t="s">
         <v>328</v>
       </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
@@ -4833,16 +4845,16 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="98" t="s">
         <v>465</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="98" t="s">
         <v>466</v>
       </c>
-      <c r="D9" s="87" t="s">
+      <c r="D9" s="98" t="s">
         <v>467</v>
       </c>
       <c r="E9" s="40">
@@ -4862,10 +4874,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="81"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
       <c r="E10" s="34">
         <v>2</v>
       </c>
@@ -4883,10 +4895,10 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="81"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="40">
         <v>3</v>
       </c>
@@ -4896,10 +4908,10 @@
       <c r="I11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="81"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
       <c r="E12" s="40">
         <v>4</v>
       </c>
@@ -4910,11 +4922,11 @@
     </row>
     <row r="13" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35"/>
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
       <c r="E13" s="35"/>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
@@ -4922,16 +4934,16 @@
       <c r="I13" s="36"/>
     </row>
     <row r="14" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="98" t="s">
         <v>468</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="98" t="s">
         <v>469</v>
       </c>
-      <c r="D14" s="87" t="s">
+      <c r="D14" s="98" t="s">
         <v>470</v>
       </c>
       <c r="E14" s="40">
@@ -4951,10 +4963,10 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81"/>
-      <c r="B15" s="88"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="88"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
       <c r="E15" s="40">
         <v>2</v>
       </c>
@@ -4972,10 +4984,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
       <c r="E16" s="40">
         <v>3</v>
       </c>
@@ -4993,10 +5005,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
       <c r="E17" s="40">
         <v>4</v>
       </c>
@@ -5007,11 +5019,11 @@
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
       <c r="E18" s="35"/>
       <c r="F18" s="36"/>
       <c r="G18" s="36"/>
@@ -5019,16 +5031,16 @@
       <c r="I18" s="36"/>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="98" t="s">
         <v>468</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="98" t="s">
         <v>471</v>
       </c>
-      <c r="D19" s="87" t="s">
+      <c r="D19" s="98" t="s">
         <v>472</v>
       </c>
       <c r="E19" s="40">
@@ -5048,10 +5060,10 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="81"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
       <c r="E20" s="40">
         <v>2</v>
       </c>
@@ -5069,10 +5081,10 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="81"/>
-      <c r="B21" s="88"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
       <c r="E21" s="40">
         <v>3</v>
       </c>
@@ -5090,10 +5102,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="81"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
       <c r="E22" s="40">
         <v>4</v>
       </c>
@@ -5104,11 +5116,11 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
       <c r="E23" s="35"/>
       <c r="F23" s="36"/>
       <c r="G23" s="36"/>
@@ -5116,16 +5128,16 @@
       <c r="I23" s="36"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="92" t="s">
         <v>473</v>
       </c>
-      <c r="C24" s="84" t="s">
+      <c r="C24" s="92" t="s">
         <v>474</v>
       </c>
-      <c r="D24" s="84" t="s">
+      <c r="D24" s="92" t="s">
         <v>475</v>
       </c>
       <c r="E24" s="40">
@@ -5145,10 +5157,10 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
+      <c r="A25" s="93"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
       <c r="E25" s="40">
         <v>2</v>
       </c>
@@ -5166,10 +5178,10 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
+      <c r="A26" s="93"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="40">
         <v>3</v>
       </c>
@@ -5187,10 +5199,10 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
+      <c r="A27" s="93"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="40">
         <v>4</v>
       </c>
@@ -5208,10 +5220,10 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="85"/>
+      <c r="A28" s="93"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="93"/>
+      <c r="D28" s="93"/>
       <c r="E28" s="40">
         <v>5</v>
       </c>
@@ -5229,10 +5241,10 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
+      <c r="A29" s="94"/>
+      <c r="B29" s="94"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
       <c r="E29" s="40">
         <v>6</v>
       </c>
@@ -5251,19 +5263,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
     <mergeCell ref="D24:D29"/>
     <mergeCell ref="C24:C29"/>
     <mergeCell ref="B24:B29"/>
@@ -5278,6 +5277,19 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5380,24 +5392,40 @@
       <c r="F3" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="53"/>
+      <c r="G3" s="53" t="s">
+        <v>30</v>
+      </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
+      <c r="I3" s="67" t="s">
+        <v>383</v>
+      </c>
+      <c r="J3" s="66" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="110" t="s">
         <v>332</v>
       </c>
       <c r="D4" s="10"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="53"/>
+      <c r="E4" s="53" t="s">
+        <v>566</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>30</v>
+      </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
+      <c r="I4" s="67" t="s">
+        <v>383</v>
+      </c>
+      <c r="J4" s="66" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
@@ -5406,7 +5434,7 @@
       <c r="B5" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="110" t="s">
         <v>356</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -5827,34 +5855,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="108"/>
-      <c r="J1" s="107" t="s">
+      <c r="H1" s="109"/>
+      <c r="J1" s="108" t="s">
         <v>346</v>
       </c>
-      <c r="K1" s="108"/>
-      <c r="M1" s="107" t="s">
+      <c r="K1" s="109"/>
+      <c r="M1" s="108" t="s">
         <v>347</v>
       </c>
-      <c r="N1" s="108"/>
-      <c r="P1" s="107" t="s">
+      <c r="N1" s="109"/>
+      <c r="P1" s="108" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="108"/>
-      <c r="S1" s="107" t="s">
+      <c r="Q1" s="109"/>
+      <c r="S1" s="108" t="s">
         <v>349</v>
       </c>
-      <c r="T1" s="108"/>
-      <c r="V1" s="107" t="s">
+      <c r="T1" s="109"/>
+      <c r="V1" s="108" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="108"/>
-      <c r="Y1" s="107" t="s">
+      <c r="W1" s="109"/>
+      <c r="Y1" s="108" t="s">
         <v>351</v>
       </c>
-      <c r="Z1" s="108"/>
+      <c r="Z1" s="109"/>
     </row>
     <row r="2" spans="1:31" s="17" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
